--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Forms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fields" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Actions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forms'!$A$3:$J$14</definedName>

--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Forms" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fields" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Actions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forms'!$A$3:$J$14</definedName>

--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Spoke</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Spoke</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Spoke</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Spoke</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Spoke</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>

--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Forms" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fields" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Actions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forms'!$A$3:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fields'!$A$3:$U$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fields'!$A$3:$U$582</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FormRelationships'!$A$3:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ReferencedDataFields'!$A$3:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflows'!$A$3:$L$5</definedName>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr"/>
@@ -1214,11 +1214,15 @@
       </c>
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>1: View All</t>
+        </is>
+      </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
@@ -1298,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U471"/>
+  <dimension ref="A1:U582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -28138,8 +28142,6865 @@
       <c r="T471" s="10" t="inlineStr"/>
       <c r="U471" s="10" t="inlineStr"/>
     </row>
+    <row r="472" ht="22" customHeight="1">
+      <c r="A472" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::CustomerName</t>
+        </is>
+      </c>
+      <c r="B472" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C472" s="10" t="inlineStr">
+        <is>
+          <t>CustomerName</t>
+        </is>
+      </c>
+      <c r="D472" s="10" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="E472" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F472" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G472" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H472" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I472" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J472" s="10" t="inlineStr"/>
+      <c r="K472" s="10" t="inlineStr"/>
+      <c r="L472" s="10" t="inlineStr"/>
+      <c r="M472" s="10" t="inlineStr"/>
+      <c r="N472" s="10" t="inlineStr"/>
+      <c r="O472" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P472" s="10" t="inlineStr"/>
+      <c r="Q472" s="10" t="inlineStr"/>
+      <c r="R472" s="10" t="inlineStr"/>
+      <c r="S472" s="10" t="inlineStr"/>
+      <c r="T472" s="10" t="inlineStr"/>
+      <c r="U472" s="10" t="inlineStr"/>
+    </row>
+    <row r="473" ht="22" customHeight="1">
+      <c r="A473" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::Notes</t>
+        </is>
+      </c>
+      <c r="B473" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C473" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D473" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E473" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F473" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G473" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H473" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I473" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J473" s="10" t="inlineStr"/>
+      <c r="K473" s="10" t="inlineStr"/>
+      <c r="L473" s="10" t="inlineStr"/>
+      <c r="M473" s="10" t="inlineStr"/>
+      <c r="N473" s="10" t="inlineStr"/>
+      <c r="O473" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P473" s="10" t="inlineStr"/>
+      <c r="Q473" s="10" t="inlineStr"/>
+      <c r="R473" s="10" t="inlineStr"/>
+      <c r="S473" s="10" t="inlineStr"/>
+      <c r="T473" s="10" t="inlineStr"/>
+      <c r="U473" s="10" t="inlineStr"/>
+    </row>
+    <row r="474" ht="22" customHeight="1">
+      <c r="A474" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::CompletedBy</t>
+        </is>
+      </c>
+      <c r="B474" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C474" s="10" t="inlineStr">
+        <is>
+          <t>CompletedBy</t>
+        </is>
+      </c>
+      <c r="D474" s="10" t="inlineStr">
+        <is>
+          <t>Completed By</t>
+        </is>
+      </c>
+      <c r="E474" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F474" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeSelect</t>
+        </is>
+      </c>
+      <c r="G474" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H474" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I474" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J474" s="10" t="inlineStr"/>
+      <c r="K474" s="10" t="inlineStr"/>
+      <c r="L474" s="10" t="inlineStr"/>
+      <c r="M474" s="10" t="inlineStr"/>
+      <c r="N474" s="10" t="inlineStr"/>
+      <c r="O474" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P474" s="10" t="inlineStr"/>
+      <c r="Q474" s="10" t="inlineStr"/>
+      <c r="R474" s="10" t="inlineStr"/>
+      <c r="S474" s="10" t="inlineStr"/>
+      <c r="T474" s="10" t="inlineStr"/>
+      <c r="U474" s="10" t="inlineStr"/>
+    </row>
+    <row r="475" ht="22" customHeight="1">
+      <c r="A475" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::EnrollmentNumber</t>
+        </is>
+      </c>
+      <c r="B475" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C475" s="10" t="inlineStr">
+        <is>
+          <t>EnrollmentNumber</t>
+        </is>
+      </c>
+      <c r="D475" s="10" t="inlineStr">
+        <is>
+          <t>Enrollment Number</t>
+        </is>
+      </c>
+      <c r="E475" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F475" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G475" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H475" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I475" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J475" s="10" t="inlineStr"/>
+      <c r="K475" s="10" t="inlineStr"/>
+      <c r="L475" s="10" t="inlineStr"/>
+      <c r="M475" s="10" t="inlineStr"/>
+      <c r="N475" s="10" t="inlineStr"/>
+      <c r="O475" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P475" s="10" t="inlineStr"/>
+      <c r="Q475" s="10" t="inlineStr"/>
+      <c r="R475" s="10" t="inlineStr"/>
+      <c r="S475" s="10" t="inlineStr"/>
+      <c r="T475" s="10" t="inlineStr"/>
+      <c r="U475" s="10" t="inlineStr"/>
+    </row>
+    <row r="476" ht="22" customHeight="1">
+      <c r="A476" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::TelephoneNumber</t>
+        </is>
+      </c>
+      <c r="B476" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C476" s="10" t="inlineStr">
+        <is>
+          <t>TelephoneNumber</t>
+        </is>
+      </c>
+      <c r="D476" s="10" t="inlineStr">
+        <is>
+          <t>Telephone Number</t>
+        </is>
+      </c>
+      <c r="E476" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F476" s="10" t="inlineStr">
+        <is>
+          <t>PhoneNumberInput</t>
+        </is>
+      </c>
+      <c r="G476" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H476" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I476" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J476" s="10" t="inlineStr"/>
+      <c r="K476" s="10" t="inlineStr"/>
+      <c r="L476" s="10" t="inlineStr"/>
+      <c r="M476" s="10" t="inlineStr"/>
+      <c r="N476" s="10" t="inlineStr"/>
+      <c r="O476" s="10" t="inlineStr">
+        <is>
+          <t>PhoneValidator</t>
+        </is>
+      </c>
+      <c r="P476" s="10" t="inlineStr"/>
+      <c r="Q476" s="10" t="inlineStr"/>
+      <c r="R476" s="10" t="inlineStr"/>
+      <c r="S476" s="10" t="inlineStr"/>
+      <c r="T476" s="10" t="inlineStr"/>
+      <c r="U476" s="10" t="inlineStr"/>
+    </row>
+    <row r="477" ht="22" customHeight="1">
+      <c r="A477" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::EmailAddress</t>
+        </is>
+      </c>
+      <c r="B477" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C477" s="10" t="inlineStr">
+        <is>
+          <t>EmailAddress</t>
+        </is>
+      </c>
+      <c r="D477" s="10" t="inlineStr">
+        <is>
+          <t>Email Address</t>
+        </is>
+      </c>
+      <c r="E477" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F477" s="10" t="inlineStr">
+        <is>
+          <t>EmailInput</t>
+        </is>
+      </c>
+      <c r="G477" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H477" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I477" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J477" s="10" t="inlineStr"/>
+      <c r="K477" s="10" t="inlineStr"/>
+      <c r="L477" s="10" t="inlineStr"/>
+      <c r="M477" s="10" t="inlineStr"/>
+      <c r="N477" s="10" t="inlineStr"/>
+      <c r="O477" s="10" t="inlineStr">
+        <is>
+          <t>EmailValidator</t>
+        </is>
+      </c>
+      <c r="P477" s="10" t="inlineStr"/>
+      <c r="Q477" s="10" t="inlineStr"/>
+      <c r="R477" s="10" t="inlineStr"/>
+      <c r="S477" s="10" t="inlineStr"/>
+      <c r="T477" s="10" t="inlineStr"/>
+      <c r="U477" s="10" t="inlineStr"/>
+    </row>
+    <row r="478" ht="22" customHeight="1">
+      <c r="A478" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::ServicesReceived</t>
+        </is>
+      </c>
+      <c r="B478" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C478" s="10" t="inlineStr">
+        <is>
+          <t>ServicesReceived</t>
+        </is>
+      </c>
+      <c r="D478" s="10" t="inlineStr">
+        <is>
+          <t>Services Received</t>
+        </is>
+      </c>
+      <c r="E478" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="F478" s="10" t="inlineStr">
+        <is>
+          <t>MultiDropDownInput</t>
+        </is>
+      </c>
+      <c r="G478" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H478" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I478" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J478" s="10" t="inlineStr"/>
+      <c r="K478" s="10" t="inlineStr"/>
+      <c r="L478" s="10" t="inlineStr"/>
+      <c r="M478" s="10" t="inlineStr"/>
+      <c r="N478" s="10" t="inlineStr"/>
+      <c r="O478" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P478" s="10" t="inlineStr"/>
+      <c r="Q478" s="10" t="inlineStr"/>
+      <c r="R478" s="10" t="inlineStr"/>
+      <c r="S478" s="10" t="inlineStr"/>
+      <c r="T478" s="10" t="inlineStr"/>
+      <c r="U478" s="10" t="inlineStr"/>
+    </row>
+    <row r="479" ht="22" customHeight="1">
+      <c r="A479" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DateContacted</t>
+        </is>
+      </c>
+      <c r="B479" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C479" s="10" t="inlineStr">
+        <is>
+          <t>DateContacted</t>
+        </is>
+      </c>
+      <c r="D479" s="10" t="inlineStr">
+        <is>
+          <t>Date Contacted</t>
+        </is>
+      </c>
+      <c r="E479" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F479" s="10" t="inlineStr">
+        <is>
+          <t>DateInput</t>
+        </is>
+      </c>
+      <c r="G479" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H479" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I479" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J479" s="10" t="inlineStr"/>
+      <c r="K479" s="10" t="inlineStr"/>
+      <c r="L479" s="10" t="inlineStr"/>
+      <c r="M479" s="10" t="inlineStr"/>
+      <c r="N479" s="10" t="inlineStr"/>
+      <c r="O479" s="10" t="inlineStr">
+        <is>
+          <t>DateValidator</t>
+        </is>
+      </c>
+      <c r="P479" s="10" t="inlineStr"/>
+      <c r="Q479" s="10" t="inlineStr"/>
+      <c r="R479" s="10" t="inlineStr"/>
+      <c r="S479" s="10" t="inlineStr"/>
+      <c r="T479" s="10" t="inlineStr"/>
+      <c r="U479" s="10" t="inlineStr"/>
+    </row>
+    <row r="480" ht="22" customHeight="1">
+      <c r="A480" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::TimeContacted</t>
+        </is>
+      </c>
+      <c r="B480" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C480" s="10" t="inlineStr">
+        <is>
+          <t>TimeContacted</t>
+        </is>
+      </c>
+      <c r="D480" s="10" t="inlineStr">
+        <is>
+          <t>Time Contacted</t>
+        </is>
+      </c>
+      <c r="E480" s="10" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="F480" s="10" t="inlineStr">
+        <is>
+          <t>TimeInput</t>
+        </is>
+      </c>
+      <c r="G480" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H480" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I480" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J480" s="10" t="inlineStr"/>
+      <c r="K480" s="10" t="inlineStr"/>
+      <c r="L480" s="10" t="inlineStr"/>
+      <c r="M480" s="10" t="inlineStr"/>
+      <c r="N480" s="10" t="inlineStr"/>
+      <c r="O480" s="10" t="inlineStr">
+        <is>
+          <t>TimeValidator</t>
+        </is>
+      </c>
+      <c r="P480" s="10" t="inlineStr"/>
+      <c r="Q480" s="10" t="inlineStr"/>
+      <c r="R480" s="10" t="inlineStr"/>
+      <c r="S480" s="10" t="inlineStr"/>
+      <c r="T480" s="10" t="inlineStr"/>
+      <c r="U480" s="10" t="inlineStr"/>
+    </row>
+    <row r="481" ht="22" customHeight="1">
+      <c r="A481" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::ContactResults</t>
+        </is>
+      </c>
+      <c r="B481" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C481" s="10" t="inlineStr">
+        <is>
+          <t>ContactResults</t>
+        </is>
+      </c>
+      <c r="D481" s="10" t="inlineStr">
+        <is>
+          <t>Contact Results</t>
+        </is>
+      </c>
+      <c r="E481" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="F481" s="10" t="inlineStr">
+        <is>
+          <t>MultiDropDownInput</t>
+        </is>
+      </c>
+      <c r="G481" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H481" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I481" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J481" s="10" t="inlineStr"/>
+      <c r="K481" s="10" t="inlineStr"/>
+      <c r="L481" s="10" t="inlineStr"/>
+      <c r="M481" s="10" t="inlineStr"/>
+      <c r="N481" s="10" t="inlineStr"/>
+      <c r="O481" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P481" s="10" t="inlineStr"/>
+      <c r="Q481" s="10" t="inlineStr"/>
+      <c r="R481" s="10" t="inlineStr"/>
+      <c r="S481" s="10" t="inlineStr"/>
+      <c r="T481" s="10" t="inlineStr"/>
+      <c r="U481" s="10" t="inlineStr"/>
+    </row>
+    <row r="482" ht="22" customHeight="1">
+      <c r="A482" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::AreYouSatisfiedWithTheSchedulingAndDelivery</t>
+        </is>
+      </c>
+      <c r="B482" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C482" s="10" t="inlineStr">
+        <is>
+          <t>AreYouSatisfiedWithTheSchedulingAndDelivery</t>
+        </is>
+      </c>
+      <c r="D482" s="10" t="inlineStr">
+        <is>
+          <t>Are you satisfied with the scheduling and delivery?</t>
+        </is>
+      </c>
+      <c r="E482" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F482" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G482" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H482" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I482" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J482" s="10" t="inlineStr"/>
+      <c r="K482" s="10" t="inlineStr"/>
+      <c r="L482" s="10" t="inlineStr"/>
+      <c r="M482" s="10" t="inlineStr"/>
+      <c r="N482" s="10" t="inlineStr"/>
+      <c r="O482" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P482" s="10" t="inlineStr"/>
+      <c r="Q482" s="10" t="inlineStr"/>
+      <c r="R482" s="10" t="inlineStr"/>
+      <c r="S482" s="10" t="inlineStr"/>
+      <c r="T482" s="10" t="inlineStr"/>
+      <c r="U482" s="10" t="inlineStr"/>
+    </row>
+    <row r="483" ht="22" customHeight="1">
+      <c r="A483" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DidYouReceiveAllTheProductsThatWereOrdered</t>
+        </is>
+      </c>
+      <c r="B483" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C483" s="10" t="inlineStr">
+        <is>
+          <t>DidYouReceiveAllTheProductsThatWereOrdered</t>
+        </is>
+      </c>
+      <c r="D483" s="10" t="inlineStr">
+        <is>
+          <t>Did you receive all the products that were ordered?</t>
+        </is>
+      </c>
+      <c r="E483" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F483" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G483" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H483" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I483" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J483" s="10" t="inlineStr"/>
+      <c r="K483" s="10" t="inlineStr"/>
+      <c r="L483" s="10" t="inlineStr"/>
+      <c r="M483" s="10" t="inlineStr"/>
+      <c r="N483" s="10" t="inlineStr"/>
+      <c r="O483" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P483" s="10" t="inlineStr"/>
+      <c r="Q483" s="10" t="inlineStr"/>
+      <c r="R483" s="10" t="inlineStr"/>
+      <c r="S483" s="10" t="inlineStr"/>
+      <c r="T483" s="10" t="inlineStr"/>
+      <c r="U483" s="10" t="inlineStr"/>
+    </row>
+    <row r="484" ht="22" customHeight="1">
+      <c r="A484" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::AreYouSatisfiedWithTheProductsYouReceived</t>
+        </is>
+      </c>
+      <c r="B484" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C484" s="10" t="inlineStr">
+        <is>
+          <t>AreYouSatisfiedWithTheProductsYouReceived</t>
+        </is>
+      </c>
+      <c r="D484" s="10" t="inlineStr">
+        <is>
+          <t>Are you satisfied with the products you received?</t>
+        </is>
+      </c>
+      <c r="E484" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F484" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G484" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H484" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I484" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J484" s="10" t="inlineStr"/>
+      <c r="K484" s="10" t="inlineStr"/>
+      <c r="L484" s="10" t="inlineStr"/>
+      <c r="M484" s="10" t="inlineStr"/>
+      <c r="N484" s="10" t="inlineStr"/>
+      <c r="O484" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P484" s="10" t="inlineStr"/>
+      <c r="Q484" s="10" t="inlineStr"/>
+      <c r="R484" s="10" t="inlineStr"/>
+      <c r="S484" s="10" t="inlineStr"/>
+      <c r="T484" s="10" t="inlineStr"/>
+      <c r="U484" s="10" t="inlineStr"/>
+    </row>
+    <row r="485" ht="22" customHeight="1">
+      <c r="A485" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WouldYouLikeToBeContactedAboutYourExperience</t>
+        </is>
+      </c>
+      <c r="B485" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C485" s="10" t="inlineStr">
+        <is>
+          <t>WouldYouLikeToBeContactedAboutYourExperience</t>
+        </is>
+      </c>
+      <c r="D485" s="10" t="inlineStr">
+        <is>
+          <t>Would you like to be contacted about your experience?</t>
+        </is>
+      </c>
+      <c r="E485" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F485" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G485" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H485" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I485" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J485" s="10" t="inlineStr"/>
+      <c r="K485" s="10" t="inlineStr"/>
+      <c r="L485" s="10" t="inlineStr"/>
+      <c r="M485" s="10" t="inlineStr"/>
+      <c r="N485" s="10" t="inlineStr"/>
+      <c r="O485" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P485" s="10" t="inlineStr"/>
+      <c r="Q485" s="10" t="inlineStr"/>
+      <c r="R485" s="10" t="inlineStr"/>
+      <c r="S485" s="10" t="inlineStr"/>
+      <c r="T485" s="10" t="inlineStr"/>
+      <c r="U485" s="10" t="inlineStr"/>
+    </row>
+    <row r="486" ht="22" customHeight="1">
+      <c r="A486" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DidTheRepresentativeInstallOrOfferToInstallTheLightBulbs</t>
+        </is>
+      </c>
+      <c r="B486" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C486" s="10" t="inlineStr">
+        <is>
+          <t>DidTheRepresentativeInstallOrOfferToInstallTheLightBulbs</t>
+        </is>
+      </c>
+      <c r="D486" s="10" t="inlineStr">
+        <is>
+          <t>Did the representative install or offer to install the light bulbs?</t>
+        </is>
+      </c>
+      <c r="E486" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F486" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G486" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H486" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I486" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J486" s="10" t="inlineStr"/>
+      <c r="K486" s="10" t="inlineStr"/>
+      <c r="L486" s="10" t="inlineStr"/>
+      <c r="M486" s="10" t="inlineStr"/>
+      <c r="N486" s="10" t="inlineStr"/>
+      <c r="O486" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P486" s="10" t="inlineStr"/>
+      <c r="Q486" s="10" t="inlineStr"/>
+      <c r="R486" s="10" t="inlineStr"/>
+      <c r="S486" s="10" t="inlineStr"/>
+      <c r="T486" s="10" t="inlineStr"/>
+      <c r="U486" s="10" t="inlineStr"/>
+    </row>
+    <row r="487" ht="22" customHeight="1">
+      <c r="A487" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WasItEasyForYouToApplyForTheQualifiedApplianceReplacementOffer</t>
+        </is>
+      </c>
+      <c r="B487" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C487" s="10" t="inlineStr">
+        <is>
+          <t>WasItEasyForYouToApplyForTheQualifiedApplianceReplacementOffer</t>
+        </is>
+      </c>
+      <c r="D487" s="10" t="inlineStr">
+        <is>
+          <t>Was it easy for you to apply for the Qualified Appliance Replacement offer?</t>
+        </is>
+      </c>
+      <c r="E487" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F487" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G487" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H487" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I487" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J487" s="10" t="inlineStr"/>
+      <c r="K487" s="10" t="inlineStr"/>
+      <c r="L487" s="10" t="inlineStr"/>
+      <c r="M487" s="10" t="inlineStr"/>
+      <c r="N487" s="10" t="inlineStr"/>
+      <c r="O487" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P487" s="10" t="inlineStr"/>
+      <c r="Q487" s="10" t="inlineStr"/>
+      <c r="R487" s="10" t="inlineStr"/>
+      <c r="S487" s="10" t="inlineStr"/>
+      <c r="T487" s="10" t="inlineStr"/>
+      <c r="U487" s="10" t="inlineStr"/>
+    </row>
+    <row r="488" ht="22" customHeight="1">
+      <c r="A488" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DidTheRepresentativeInstallOrOfferToInstallTheAdvancedPowerStrip</t>
+        </is>
+      </c>
+      <c r="B488" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C488" s="10" t="inlineStr">
+        <is>
+          <t>DidTheRepresentativeInstallOrOfferToInstallTheAdvancedPowerStrip</t>
+        </is>
+      </c>
+      <c r="D488" s="10" t="inlineStr">
+        <is>
+          <t>Did the representative install or offer to install the advanced power strip?</t>
+        </is>
+      </c>
+      <c r="E488" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F488" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G488" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H488" s="10" t="inlineStr"/>
+      <c r="I488" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J488" s="10" t="inlineStr"/>
+      <c r="K488" s="10" t="inlineStr"/>
+      <c r="L488" s="10" t="inlineStr"/>
+      <c r="M488" s="10" t="inlineStr"/>
+      <c r="N488" s="10" t="inlineStr"/>
+      <c r="O488" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P488" s="10" t="inlineStr"/>
+      <c r="Q488" s="10" t="inlineStr"/>
+      <c r="R488" s="10" t="inlineStr"/>
+      <c r="S488" s="10" t="inlineStr"/>
+      <c r="T488" s="10" t="inlineStr"/>
+      <c r="U488" s="10" t="inlineStr"/>
+    </row>
+    <row r="489" ht="22" customHeight="1">
+      <c r="A489" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::SpokeTo</t>
+        </is>
+      </c>
+      <c r="B489" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C489" s="10" t="inlineStr">
+        <is>
+          <t>SpokeTo</t>
+        </is>
+      </c>
+      <c r="D489" s="10" t="inlineStr">
+        <is>
+          <t>Spoke To</t>
+        </is>
+      </c>
+      <c r="E489" s="10" t="inlineStr">
+        <is>
+          <t>Guid</t>
+        </is>
+      </c>
+      <c r="F489" s="10" t="inlineStr">
+        <is>
+          <t>UserSelect</t>
+        </is>
+      </c>
+      <c r="G489" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H489" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I489" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J489" s="10" t="inlineStr"/>
+      <c r="K489" s="10" t="inlineStr"/>
+      <c r="L489" s="10" t="inlineStr"/>
+      <c r="M489" s="10" t="inlineStr"/>
+      <c r="N489" s="10" t="inlineStr"/>
+      <c r="O489" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P489" s="10" t="inlineStr"/>
+      <c r="Q489" s="10" t="inlineStr"/>
+      <c r="R489" s="10" t="inlineStr"/>
+      <c r="S489" s="10" t="inlineStr"/>
+      <c r="T489" s="10" t="inlineStr"/>
+      <c r="U489" s="10" t="inlineStr"/>
+    </row>
+    <row r="490" ht="22" customHeight="1">
+      <c r="A490" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::NotSatisfiedWithTheProductsExplain</t>
+        </is>
+      </c>
+      <c r="B490" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C490" s="10" t="inlineStr">
+        <is>
+          <t>NotSatisfiedWithTheProductsExplain</t>
+        </is>
+      </c>
+      <c r="D490" s="10" t="inlineStr">
+        <is>
+          <t>If No, Please Explain</t>
+        </is>
+      </c>
+      <c r="E490" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F490" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G490" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H490" s="10" t="inlineStr"/>
+      <c r="I490" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J490" s="10" t="inlineStr"/>
+      <c r="K490" s="10" t="inlineStr"/>
+      <c r="L490" s="10" t="inlineStr"/>
+      <c r="M490" s="10" t="inlineStr"/>
+      <c r="N490" s="10" t="inlineStr"/>
+      <c r="O490" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P490" s="10" t="inlineStr"/>
+      <c r="Q490" s="10" t="inlineStr"/>
+      <c r="R490" s="10" t="inlineStr"/>
+      <c r="S490" s="10" t="inlineStr"/>
+      <c r="T490" s="10" t="inlineStr"/>
+      <c r="U490" s="10" t="inlineStr"/>
+    </row>
+    <row r="491" ht="22" customHeight="1">
+      <c r="A491" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhatDevicesDoYouHavePluggedIntoTheNewAdvancedPowerStrip</t>
+        </is>
+      </c>
+      <c r="B491" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C491" s="10" t="inlineStr">
+        <is>
+          <t>WhatDevicesDoYouHavePluggedIntoTheNewAdvancedPowerStrip</t>
+        </is>
+      </c>
+      <c r="D491" s="10" t="inlineStr">
+        <is>
+          <t>What devices do you have plugged into the new advanced power strip?</t>
+        </is>
+      </c>
+      <c r="E491" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="F491" s="10" t="inlineStr">
+        <is>
+          <t>MultiDropDownInput</t>
+        </is>
+      </c>
+      <c r="G491" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H491" s="10" t="inlineStr"/>
+      <c r="I491" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J491" s="10" t="inlineStr"/>
+      <c r="K491" s="10" t="inlineStr"/>
+      <c r="L491" s="10" t="inlineStr"/>
+      <c r="M491" s="10" t="inlineStr"/>
+      <c r="N491" s="10" t="inlineStr"/>
+      <c r="O491" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P491" s="10" t="inlineStr"/>
+      <c r="Q491" s="10" t="inlineStr"/>
+      <c r="R491" s="10" t="inlineStr"/>
+      <c r="S491" s="10" t="inlineStr"/>
+      <c r="T491" s="10" t="inlineStr"/>
+      <c r="U491" s="10" t="inlineStr"/>
+    </row>
+    <row r="492" ht="22" customHeight="1">
+      <c r="A492" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::AdditionalComments</t>
+        </is>
+      </c>
+      <c r="B492" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C492" s="10" t="inlineStr">
+        <is>
+          <t>AdditionalComments</t>
+        </is>
+      </c>
+      <c r="D492" s="10" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="E492" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F492" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G492" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H492" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I492" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J492" s="10" t="inlineStr"/>
+      <c r="K492" s="10" t="inlineStr"/>
+      <c r="L492" s="10" t="inlineStr"/>
+      <c r="M492" s="10" t="inlineStr"/>
+      <c r="N492" s="10" t="inlineStr"/>
+      <c r="O492" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P492" s="10" t="inlineStr"/>
+      <c r="Q492" s="10" t="inlineStr"/>
+      <c r="R492" s="10" t="inlineStr"/>
+      <c r="S492" s="10" t="inlineStr"/>
+      <c r="T492" s="10" t="inlineStr"/>
+      <c r="U492" s="10" t="inlineStr"/>
+    </row>
+    <row r="493" ht="22" customHeight="1">
+      <c r="A493" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::IfNoWhichItemsWereNotReceived</t>
+        </is>
+      </c>
+      <c r="B493" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C493" s="10" t="inlineStr">
+        <is>
+          <t>IfNoWhichItemsWereNotReceived</t>
+        </is>
+      </c>
+      <c r="D493" s="10" t="inlineStr">
+        <is>
+          <t>If No, which items were not received?</t>
+        </is>
+      </c>
+      <c r="E493" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="F493" s="10" t="inlineStr">
+        <is>
+          <t>MultiDropDownInput</t>
+        </is>
+      </c>
+      <c r="G493" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H493" s="10" t="inlineStr"/>
+      <c r="I493" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J493" s="10" t="inlineStr"/>
+      <c r="K493" s="10" t="inlineStr"/>
+      <c r="L493" s="10" t="inlineStr"/>
+      <c r="M493" s="10" t="inlineStr"/>
+      <c r="N493" s="10" t="inlineStr"/>
+      <c r="O493" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P493" s="10" t="inlineStr"/>
+      <c r="Q493" s="10" t="inlineStr"/>
+      <c r="R493" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S493" s="10" t="inlineStr"/>
+      <c r="T493" s="10" t="inlineStr"/>
+      <c r="U493" s="10" t="inlineStr"/>
+    </row>
+    <row r="494" ht="22" customHeight="1">
+      <c r="A494" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WasItEasyForYoutToApplyIfNoPleaseExplain</t>
+        </is>
+      </c>
+      <c r="B494" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C494" s="10" t="inlineStr">
+        <is>
+          <t>WasItEasyForYoutToApplyIfNoPleaseExplain</t>
+        </is>
+      </c>
+      <c r="D494" s="10" t="inlineStr">
+        <is>
+          <t>If No, Please Explain</t>
+        </is>
+      </c>
+      <c r="E494" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F494" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G494" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H494" s="10" t="inlineStr"/>
+      <c r="I494" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J494" s="10" t="inlineStr"/>
+      <c r="K494" s="10" t="inlineStr"/>
+      <c r="L494" s="10" t="inlineStr"/>
+      <c r="M494" s="10" t="inlineStr"/>
+      <c r="N494" s="10" t="inlineStr"/>
+      <c r="O494" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P494" s="10" t="inlineStr"/>
+      <c r="Q494" s="10" t="inlineStr"/>
+      <c r="R494" s="10" t="inlineStr"/>
+      <c r="S494" s="10" t="inlineStr"/>
+      <c r="T494" s="10" t="inlineStr"/>
+      <c r="U494" s="10" t="inlineStr"/>
+    </row>
+    <row r="495" ht="22" customHeight="1">
+      <c r="A495" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowManyLedLightBulbsDidTheRepresentativeInstall</t>
+        </is>
+      </c>
+      <c r="B495" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C495" s="10" t="inlineStr">
+        <is>
+          <t>HowManyLedLightBulbsDidTheRepresentativeInstall</t>
+        </is>
+      </c>
+      <c r="D495" s="10" t="inlineStr">
+        <is>
+          <t>How many LED light bulbs did the representative install?</t>
+        </is>
+      </c>
+      <c r="E495" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F495" s="10" t="inlineStr">
+        <is>
+          <t>NumberInput</t>
+        </is>
+      </c>
+      <c r="G495" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H495" s="10" t="inlineStr"/>
+      <c r="I495" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J495" s="10" t="inlineStr"/>
+      <c r="K495" s="10" t="inlineStr"/>
+      <c r="L495" s="10" t="inlineStr"/>
+      <c r="M495" s="10" t="inlineStr"/>
+      <c r="N495" s="10" t="inlineStr"/>
+      <c r="O495" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P495" s="10" t="inlineStr"/>
+      <c r="Q495" s="10" t="inlineStr"/>
+      <c r="R495" s="10" t="inlineStr"/>
+      <c r="S495" s="10" t="inlineStr"/>
+      <c r="T495" s="10" t="inlineStr"/>
+      <c r="U495" s="10" t="inlineStr"/>
+    </row>
+    <row r="496" ht="22" customHeight="1">
+      <c r="A496" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::AreYouSatisfiedWithTheSchedulingAndDeliveryIfNoPleaseExplain</t>
+        </is>
+      </c>
+      <c r="B496" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C496" s="10" t="inlineStr">
+        <is>
+          <t>AreYouSatisfiedWithTheSchedulingAndDeliveryIfNoPleaseExplain</t>
+        </is>
+      </c>
+      <c r="D496" s="10" t="inlineStr">
+        <is>
+          <t>If No, Please Explain</t>
+        </is>
+      </c>
+      <c r="E496" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F496" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G496" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H496" s="10" t="inlineStr"/>
+      <c r="I496" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J496" s="10" t="inlineStr"/>
+      <c r="K496" s="10" t="inlineStr"/>
+      <c r="L496" s="10" t="inlineStr"/>
+      <c r="M496" s="10" t="inlineStr"/>
+      <c r="N496" s="10" t="inlineStr"/>
+      <c r="O496" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P496" s="10" t="inlineStr"/>
+      <c r="Q496" s="10" t="inlineStr"/>
+      <c r="R496" s="10" t="inlineStr"/>
+      <c r="S496" s="10" t="inlineStr"/>
+      <c r="T496" s="10" t="inlineStr"/>
+      <c r="U496" s="10" t="inlineStr"/>
+    </row>
+    <row r="497" ht="22" customHeight="1">
+      <c r="A497" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhatKindOfLedOfBulbsWereReplaced</t>
+        </is>
+      </c>
+      <c r="B497" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C497" s="10" t="inlineStr">
+        <is>
+          <t>WhatKindOfLedOfBulbsWereReplaced</t>
+        </is>
+      </c>
+      <c r="D497" s="10" t="inlineStr">
+        <is>
+          <t>What kind of LED of bulbs were replaced?</t>
+        </is>
+      </c>
+      <c r="E497" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="F497" s="10" t="inlineStr">
+        <is>
+          <t>MultiDropDownInput</t>
+        </is>
+      </c>
+      <c r="G497" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H497" s="10" t="inlineStr"/>
+      <c r="I497" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J497" s="10" t="inlineStr"/>
+      <c r="K497" s="10" t="inlineStr"/>
+      <c r="L497" s="10" t="inlineStr"/>
+      <c r="M497" s="10" t="inlineStr"/>
+      <c r="N497" s="10" t="inlineStr"/>
+      <c r="O497" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P497" s="10" t="inlineStr"/>
+      <c r="Q497" s="10" t="inlineStr"/>
+      <c r="R497" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S497" s="10" t="inlineStr"/>
+      <c r="T497" s="10" t="inlineStr"/>
+      <c r="U497" s="10" t="inlineStr"/>
+    </row>
+    <row r="498" ht="22" customHeight="1">
+      <c r="A498" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::OtherDevices</t>
+        </is>
+      </c>
+      <c r="B498" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C498" s="10" t="inlineStr">
+        <is>
+          <t>OtherDevices</t>
+        </is>
+      </c>
+      <c r="D498" s="10" t="inlineStr">
+        <is>
+          <t>Other (Specify)</t>
+        </is>
+      </c>
+      <c r="E498" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F498" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G498" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H498" s="10" t="inlineStr"/>
+      <c r="I498" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J498" s="10" t="inlineStr"/>
+      <c r="K498" s="10" t="inlineStr"/>
+      <c r="L498" s="10" t="inlineStr"/>
+      <c r="M498" s="10" t="inlineStr"/>
+      <c r="N498" s="10" t="inlineStr"/>
+      <c r="O498" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P498" s="10" t="inlineStr"/>
+      <c r="Q498" s="10" t="inlineStr"/>
+      <c r="R498" s="10" t="inlineStr"/>
+      <c r="S498" s="10" t="inlineStr"/>
+      <c r="T498" s="10" t="inlineStr"/>
+      <c r="U498" s="10" t="inlineStr"/>
+    </row>
+    <row r="499" ht="22" customHeight="1">
+      <c r="A499" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhichProductsDidYouOrder</t>
+        </is>
+      </c>
+      <c r="B499" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C499" s="10" t="inlineStr">
+        <is>
+          <t>WhichProductsDidYouOrder</t>
+        </is>
+      </c>
+      <c r="D499" s="10" t="inlineStr">
+        <is>
+          <t>Which products did you order?</t>
+        </is>
+      </c>
+      <c r="E499" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="F499" s="10" t="inlineStr">
+        <is>
+          <t>MultiDropDownInput</t>
+        </is>
+      </c>
+      <c r="G499" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H499" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I499" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J499" s="10" t="inlineStr"/>
+      <c r="K499" s="10" t="inlineStr"/>
+      <c r="L499" s="10" t="inlineStr"/>
+      <c r="M499" s="10" t="inlineStr"/>
+      <c r="N499" s="10" t="inlineStr"/>
+      <c r="O499" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P499" s="10" t="inlineStr"/>
+      <c r="Q499" s="10" t="inlineStr"/>
+      <c r="R499" s="10" t="inlineStr"/>
+      <c r="S499" s="10" t="inlineStr"/>
+      <c r="T499" s="10" t="inlineStr"/>
+      <c r="U499" s="10" t="inlineStr"/>
+    </row>
+    <row r="500" ht="22" customHeight="1">
+      <c r="A500" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateTheLevelOfserviceYouReceivedFromOurOfficeStaff</t>
+        </is>
+      </c>
+      <c r="B500" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C500" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateTheLevelOfserviceYouReceivedFromOurOfficeStaff</t>
+        </is>
+      </c>
+      <c r="D500" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate the level of service you received from our office staff?</t>
+        </is>
+      </c>
+      <c r="E500" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F500" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G500" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H500" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I500" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J500" s="10" t="inlineStr"/>
+      <c r="K500" s="10" t="inlineStr"/>
+      <c r="L500" s="10" t="inlineStr"/>
+      <c r="M500" s="10" t="inlineStr"/>
+      <c r="N500" s="10" t="inlineStr"/>
+      <c r="O500" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P500" s="10" t="inlineStr"/>
+      <c r="Q500" s="10" t="inlineStr"/>
+      <c r="R500" s="10" t="inlineStr"/>
+      <c r="S500" s="10" t="inlineStr"/>
+      <c r="T500" s="10" t="inlineStr"/>
+      <c r="U500" s="10" t="inlineStr"/>
+    </row>
+    <row r="501" ht="22" customHeight="1">
+      <c r="A501" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateThePhoneRepresentativesWillingnessToExplainOurServices</t>
+        </is>
+      </c>
+      <c r="B501" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C501" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateThePhoneRepresentativesWillingnessToExplainOurServices</t>
+        </is>
+      </c>
+      <c r="D501" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate the phone representative's willingness to explain our services?</t>
+        </is>
+      </c>
+      <c r="E501" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F501" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G501" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H501" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I501" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J501" s="10" t="inlineStr"/>
+      <c r="K501" s="10" t="inlineStr"/>
+      <c r="L501" s="10" t="inlineStr"/>
+      <c r="M501" s="10" t="inlineStr"/>
+      <c r="N501" s="10" t="inlineStr"/>
+      <c r="O501" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P501" s="10" t="inlineStr"/>
+      <c r="Q501" s="10" t="inlineStr"/>
+      <c r="R501" s="10" t="inlineStr"/>
+      <c r="S501" s="10" t="inlineStr"/>
+      <c r="T501" s="10" t="inlineStr"/>
+      <c r="U501" s="10" t="inlineStr"/>
+    </row>
+    <row r="502" ht="22" customHeight="1">
+      <c r="A502" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldyouRateThePresentationOfTheFieldRepresentativeSGreetingPolitenessAppearanceEtc</t>
+        </is>
+      </c>
+      <c r="B502" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C502" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldyouRateThePresentationOfTheFieldRepresentativeSGreetingPolitenessAppearanceEtc</t>
+        </is>
+      </c>
+      <c r="D502" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate the presentation of the Field Representative(s): Greeting, Politeness, appearance, etc?</t>
+        </is>
+      </c>
+      <c r="E502" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F502" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G502" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H502" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I502" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J502" s="10" t="inlineStr"/>
+      <c r="K502" s="10" t="inlineStr"/>
+      <c r="L502" s="10" t="inlineStr"/>
+      <c r="M502" s="10" t="inlineStr"/>
+      <c r="N502" s="10" t="inlineStr"/>
+      <c r="O502" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P502" s="10" t="inlineStr"/>
+      <c r="Q502" s="10" t="inlineStr"/>
+      <c r="R502" s="10" t="inlineStr"/>
+      <c r="S502" s="10" t="inlineStr"/>
+      <c r="T502" s="10" t="inlineStr"/>
+      <c r="U502" s="10" t="inlineStr"/>
+    </row>
+    <row r="503" ht="22" customHeight="1">
+      <c r="A503" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateTheQualityOfServicesAndProductsReceivedEquipmentMaterialsAppliancesEtc</t>
+        </is>
+      </c>
+      <c r="B503" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C503" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateTheQualityOfServicesAndProductsReceivedEquipmentMaterialsAppliancesEtc</t>
+        </is>
+      </c>
+      <c r="D503" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate the quality of services and products received (equipment, materials, appliances, etc)?</t>
+        </is>
+      </c>
+      <c r="E503" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F503" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G503" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H503" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I503" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J503" s="10" t="inlineStr"/>
+      <c r="K503" s="10" t="inlineStr"/>
+      <c r="L503" s="10" t="inlineStr"/>
+      <c r="M503" s="10" t="inlineStr"/>
+      <c r="N503" s="10" t="inlineStr"/>
+      <c r="O503" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P503" s="10" t="inlineStr"/>
+      <c r="Q503" s="10" t="inlineStr"/>
+      <c r="R503" s="10" t="inlineStr"/>
+      <c r="S503" s="10" t="inlineStr"/>
+      <c r="T503" s="10" t="inlineStr"/>
+      <c r="U503" s="10" t="inlineStr"/>
+    </row>
+    <row r="504" ht="22" customHeight="1">
+      <c r="A504" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateTheFieldRepresentativesExplanation</t>
+        </is>
+      </c>
+      <c r="B504" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C504" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateTheFieldRepresentativesExplanation</t>
+        </is>
+      </c>
+      <c r="D504" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate the Field Representative's explanation of how to operate the new equipment (i.e. advanced power strip, appliance, thermostat)?</t>
+        </is>
+      </c>
+      <c r="E504" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F504" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G504" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H504" s="10" t="inlineStr"/>
+      <c r="I504" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J504" s="10" t="inlineStr"/>
+      <c r="K504" s="10" t="inlineStr"/>
+      <c r="L504" s="10" t="inlineStr"/>
+      <c r="M504" s="10" t="inlineStr"/>
+      <c r="N504" s="10" t="inlineStr"/>
+      <c r="O504" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P504" s="10" t="inlineStr"/>
+      <c r="Q504" s="10" t="inlineStr"/>
+      <c r="R504" s="10" t="inlineStr"/>
+      <c r="S504" s="10" t="inlineStr"/>
+      <c r="T504" s="10" t="inlineStr"/>
+      <c r="U504" s="10" t="inlineStr"/>
+    </row>
+    <row r="505" ht="22" customHeight="1">
+      <c r="A505" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateTheFieldRepresentativesExplanationOfTheWarranty</t>
+        </is>
+      </c>
+      <c r="B505" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C505" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateTheFieldRepresentativesExplanationOfTheWarranty</t>
+        </is>
+      </c>
+      <c r="D505" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate the Field Representative's explanation of the warranty?</t>
+        </is>
+      </c>
+      <c r="E505" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F505" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G505" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H505" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I505" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J505" s="10" t="inlineStr"/>
+      <c r="K505" s="10" t="inlineStr"/>
+      <c r="L505" s="10" t="inlineStr"/>
+      <c r="M505" s="10" t="inlineStr"/>
+      <c r="N505" s="10" t="inlineStr"/>
+      <c r="O505" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P505" s="10" t="inlineStr"/>
+      <c r="Q505" s="10" t="inlineStr"/>
+      <c r="R505" s="10" t="inlineStr"/>
+      <c r="S505" s="10" t="inlineStr"/>
+      <c r="T505" s="10" t="inlineStr"/>
+      <c r="U505" s="10" t="inlineStr"/>
+    </row>
+    <row r="506" ht="22" customHeight="1">
+      <c r="A506" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateHowCleanTheFieldRepresentativesmaintainedTheWorksite</t>
+        </is>
+      </c>
+      <c r="B506" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C506" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateHowCleanTheFieldRepresentativesmaintainedTheWorksite</t>
+        </is>
+      </c>
+      <c r="D506" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate how clean the Field Representative(s) maintained the worksite?</t>
+        </is>
+      </c>
+      <c r="E506" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F506" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G506" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H506" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I506" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J506" s="10" t="inlineStr"/>
+      <c r="K506" s="10" t="inlineStr"/>
+      <c r="L506" s="10" t="inlineStr"/>
+      <c r="M506" s="10" t="inlineStr"/>
+      <c r="N506" s="10" t="inlineStr"/>
+      <c r="O506" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P506" s="10" t="inlineStr"/>
+      <c r="Q506" s="10" t="inlineStr"/>
+      <c r="R506" s="10" t="inlineStr"/>
+      <c r="S506" s="10" t="inlineStr"/>
+      <c r="T506" s="10" t="inlineStr"/>
+      <c r="U506" s="10" t="inlineStr"/>
+    </row>
+    <row r="507" ht="22" customHeight="1">
+      <c r="A507" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowWouldYouRateYourOverallExperienceWithPowerShiftByNvEnergy</t>
+        </is>
+      </c>
+      <c r="B507" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C507" s="10" t="inlineStr">
+        <is>
+          <t>HowWouldYouRateYourOverallExperienceWithPowerShiftByNvEnergy</t>
+        </is>
+      </c>
+      <c r="D507" s="10" t="inlineStr">
+        <is>
+          <t>How would you rate your overall experience with PowerShift by NV Energy?</t>
+        </is>
+      </c>
+      <c r="E507" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F507" s="10" t="inlineStr">
+        <is>
+          <t>RatingInput</t>
+        </is>
+      </c>
+      <c r="G507" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H507" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I507" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J507" s="10" t="inlineStr"/>
+      <c r="K507" s="10" t="inlineStr"/>
+      <c r="L507" s="10" t="inlineStr"/>
+      <c r="M507" s="10" t="inlineStr"/>
+      <c r="N507" s="10" t="inlineStr"/>
+      <c r="O507" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P507" s="10" t="inlineStr"/>
+      <c r="Q507" s="10" t="inlineStr"/>
+      <c r="R507" s="10" t="inlineStr"/>
+      <c r="S507" s="10" t="inlineStr"/>
+      <c r="T507" s="10" t="inlineStr"/>
+      <c r="U507" s="10" t="inlineStr"/>
+    </row>
+    <row r="508" ht="22" customHeight="1">
+      <c r="A508" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DidTheRepresentativeInstallOrOfferToInstallTheDuskToDawnLightingControlPhotocellLedSensor</t>
+        </is>
+      </c>
+      <c r="B508" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C508" s="10" t="inlineStr">
+        <is>
+          <t>DidTheRepresentativeInstallOrOfferToInstallTheDuskToDawnLightingControlPhotocellLedSensor</t>
+        </is>
+      </c>
+      <c r="D508" s="10" t="inlineStr">
+        <is>
+          <t>Did the representative install or offer to install the dusk to dawn lighting control (photocell LED sensor)?</t>
+        </is>
+      </c>
+      <c r="E508" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F508" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G508" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H508" s="10" t="inlineStr"/>
+      <c r="I508" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J508" s="10" t="inlineStr"/>
+      <c r="K508" s="10" t="inlineStr"/>
+      <c r="L508" s="10" t="inlineStr"/>
+      <c r="M508" s="10" t="inlineStr"/>
+      <c r="N508" s="10" t="inlineStr"/>
+      <c r="O508" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P508" s="10" t="inlineStr"/>
+      <c r="Q508" s="10" t="inlineStr"/>
+      <c r="R508" s="10" t="inlineStr"/>
+      <c r="S508" s="10" t="inlineStr"/>
+      <c r="T508" s="10" t="inlineStr"/>
+      <c r="U508" s="10" t="inlineStr"/>
+    </row>
+    <row r="509" ht="22" customHeight="1">
+      <c r="A509" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DidTheRepresentativeAskYouForAnyFormOfPayment</t>
+        </is>
+      </c>
+      <c r="B509" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C509" s="10" t="inlineStr">
+        <is>
+          <t>DidTheRepresentativeAskYouForAnyFormOfPayment</t>
+        </is>
+      </c>
+      <c r="D509" s="10" t="inlineStr">
+        <is>
+          <t>Did the representative ask you for any form of payment?</t>
+        </is>
+      </c>
+      <c r="E509" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F509" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G509" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H509" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I509" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J509" s="10" t="inlineStr"/>
+      <c r="K509" s="10" t="inlineStr"/>
+      <c r="L509" s="10" t="inlineStr"/>
+      <c r="M509" s="10" t="inlineStr"/>
+      <c r="N509" s="10" t="inlineStr"/>
+      <c r="O509" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P509" s="10" t="inlineStr"/>
+      <c r="Q509" s="10" t="inlineStr"/>
+      <c r="R509" s="10" t="inlineStr"/>
+      <c r="S509" s="10" t="inlineStr"/>
+      <c r="T509" s="10" t="inlineStr"/>
+      <c r="U509" s="10" t="inlineStr"/>
+    </row>
+    <row r="510" ht="22" customHeight="1">
+      <c r="A510" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhatOtherNoCostServicesWouldYouFindUseful</t>
+        </is>
+      </c>
+      <c r="B510" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C510" s="10" t="inlineStr">
+        <is>
+          <t>WhatOtherNoCostServicesWouldYouFindUseful</t>
+        </is>
+      </c>
+      <c r="D510" s="10" t="inlineStr">
+        <is>
+          <t>What other no-cost services would you find useful?</t>
+        </is>
+      </c>
+      <c r="E510" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F510" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G510" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H510" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I510" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J510" s="10" t="inlineStr"/>
+      <c r="K510" s="10" t="inlineStr"/>
+      <c r="L510" s="10" t="inlineStr"/>
+      <c r="M510" s="10" t="inlineStr"/>
+      <c r="N510" s="10" t="inlineStr"/>
+      <c r="O510" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P510" s="10" t="inlineStr"/>
+      <c r="Q510" s="10" t="inlineStr"/>
+      <c r="R510" s="10" t="inlineStr"/>
+      <c r="S510" s="10" t="inlineStr"/>
+      <c r="T510" s="10" t="inlineStr"/>
+      <c r="U510" s="10" t="inlineStr"/>
+    </row>
+    <row r="511" ht="22" customHeight="1">
+      <c r="A511" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowLikelyAreYouToReferUsToAFriend</t>
+        </is>
+      </c>
+      <c r="B511" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C511" s="10" t="inlineStr">
+        <is>
+          <t>HowLikelyAreYouToReferUsToAFriend</t>
+        </is>
+      </c>
+      <c r="D511" s="10" t="inlineStr">
+        <is>
+          <t>How likely are you to refer us to a friend?</t>
+        </is>
+      </c>
+      <c r="E511" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F511" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G511" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H511" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I511" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J511" s="10" t="inlineStr"/>
+      <c r="K511" s="10" t="inlineStr"/>
+      <c r="L511" s="10" t="inlineStr"/>
+      <c r="M511" s="10" t="inlineStr"/>
+      <c r="N511" s="10" t="inlineStr"/>
+      <c r="O511" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P511" s="10" t="inlineStr"/>
+      <c r="Q511" s="10" t="inlineStr"/>
+      <c r="R511" s="10" t="inlineStr"/>
+      <c r="S511" s="10" t="inlineStr"/>
+      <c r="T511" s="10" t="inlineStr"/>
+      <c r="U511" s="10" t="inlineStr"/>
+    </row>
+    <row r="512" ht="22" customHeight="1">
+      <c r="A512" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhatFuelDoesYourMainWaterHeaterUse</t>
+        </is>
+      </c>
+      <c r="B512" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C512" s="10" t="inlineStr">
+        <is>
+          <t>WhatFuelDoesYourMainWaterHeaterUse</t>
+        </is>
+      </c>
+      <c r="D512" s="10" t="inlineStr">
+        <is>
+          <t>What fuel does your main water heater use?</t>
+        </is>
+      </c>
+      <c r="E512" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F512" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G512" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H512" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I512" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J512" s="10" t="inlineStr"/>
+      <c r="K512" s="10" t="inlineStr"/>
+      <c r="L512" s="10" t="inlineStr"/>
+      <c r="M512" s="10" t="inlineStr"/>
+      <c r="N512" s="10" t="inlineStr"/>
+      <c r="O512" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P512" s="10" t="inlineStr"/>
+      <c r="Q512" s="10" t="inlineStr"/>
+      <c r="R512" s="10" t="inlineStr"/>
+      <c r="S512" s="10" t="inlineStr"/>
+      <c r="T512" s="10" t="inlineStr"/>
+      <c r="U512" s="10" t="inlineStr"/>
+    </row>
+    <row r="513" ht="22" customHeight="1">
+      <c r="A513" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhichOfTheFollowingBestDescribesYourHome</t>
+        </is>
+      </c>
+      <c r="B513" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C513" s="10" t="inlineStr">
+        <is>
+          <t>WhichOfTheFollowingBestDescribesYourHome</t>
+        </is>
+      </c>
+      <c r="D513" s="10" t="inlineStr">
+        <is>
+          <t>Which of the following best describes your home?</t>
+        </is>
+      </c>
+      <c r="E513" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F513" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G513" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H513" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I513" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J513" s="10" t="inlineStr"/>
+      <c r="K513" s="10" t="inlineStr"/>
+      <c r="L513" s="10" t="inlineStr"/>
+      <c r="M513" s="10" t="inlineStr"/>
+      <c r="N513" s="10" t="inlineStr"/>
+      <c r="O513" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P513" s="10" t="inlineStr"/>
+      <c r="Q513" s="10" t="inlineStr"/>
+      <c r="R513" s="10" t="inlineStr"/>
+      <c r="S513" s="10" t="inlineStr"/>
+      <c r="T513" s="10" t="inlineStr"/>
+      <c r="U513" s="10" t="inlineStr"/>
+    </row>
+    <row r="514" ht="22" customHeight="1">
+      <c r="A514" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhatIsTheMainFuelUsedToHeatYourHome</t>
+        </is>
+      </c>
+      <c r="B514" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C514" s="10" t="inlineStr">
+        <is>
+          <t>WhatIsTheMainFuelUsedToHeatYourHome</t>
+        </is>
+      </c>
+      <c r="D514" s="10" t="inlineStr">
+        <is>
+          <t>What is the main fuel used to heat your home?</t>
+        </is>
+      </c>
+      <c r="E514" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F514" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G514" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H514" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I514" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J514" s="10" t="inlineStr"/>
+      <c r="K514" s="10" t="inlineStr"/>
+      <c r="L514" s="10" t="inlineStr"/>
+      <c r="M514" s="10" t="inlineStr"/>
+      <c r="N514" s="10" t="inlineStr"/>
+      <c r="O514" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P514" s="10" t="inlineStr"/>
+      <c r="Q514" s="10" t="inlineStr"/>
+      <c r="R514" s="10" t="inlineStr"/>
+      <c r="S514" s="10" t="inlineStr"/>
+      <c r="T514" s="10" t="inlineStr"/>
+      <c r="U514" s="10" t="inlineStr"/>
+    </row>
+    <row r="515" ht="22" customHeight="1">
+      <c r="A515" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::OtherWaterHeater</t>
+        </is>
+      </c>
+      <c r="B515" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C515" s="10" t="inlineStr">
+        <is>
+          <t>OtherWaterHeater</t>
+        </is>
+      </c>
+      <c r="D515" s="10" t="inlineStr">
+        <is>
+          <t>Other - Water Heater</t>
+        </is>
+      </c>
+      <c r="E515" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F515" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G515" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H515" s="10" t="inlineStr"/>
+      <c r="I515" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J515" s="10" t="inlineStr"/>
+      <c r="K515" s="10" t="inlineStr"/>
+      <c r="L515" s="10" t="inlineStr"/>
+      <c r="M515" s="10" t="inlineStr"/>
+      <c r="N515" s="10" t="inlineStr"/>
+      <c r="O515" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P515" s="10" t="inlineStr"/>
+      <c r="Q515" s="10" t="inlineStr"/>
+      <c r="R515" s="10" t="inlineStr"/>
+      <c r="S515" s="10" t="inlineStr"/>
+      <c r="T515" s="10" t="inlineStr"/>
+      <c r="U515" s="10" t="inlineStr"/>
+    </row>
+    <row r="516" ht="22" customHeight="1">
+      <c r="A516" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::OtherHomeHeat</t>
+        </is>
+      </c>
+      <c r="B516" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C516" s="10" t="inlineStr">
+        <is>
+          <t>OtherHomeHeat</t>
+        </is>
+      </c>
+      <c r="D516" s="10" t="inlineStr">
+        <is>
+          <t>Other - Home Heat</t>
+        </is>
+      </c>
+      <c r="E516" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F516" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G516" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H516" s="10" t="inlineStr"/>
+      <c r="I516" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J516" s="10" t="inlineStr"/>
+      <c r="K516" s="10" t="inlineStr"/>
+      <c r="L516" s="10" t="inlineStr"/>
+      <c r="M516" s="10" t="inlineStr"/>
+      <c r="N516" s="10" t="inlineStr"/>
+      <c r="O516" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P516" s="10" t="inlineStr"/>
+      <c r="Q516" s="10" t="inlineStr"/>
+      <c r="R516" s="10" t="inlineStr"/>
+      <c r="S516" s="10" t="inlineStr"/>
+      <c r="T516" s="10" t="inlineStr"/>
+      <c r="U516" s="10" t="inlineStr"/>
+    </row>
+    <row r="517" ht="22" customHeight="1">
+      <c r="A517" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::DwellingTypeOther</t>
+        </is>
+      </c>
+      <c r="B517" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C517" s="10" t="inlineStr">
+        <is>
+          <t>DwellingTypeOther</t>
+        </is>
+      </c>
+      <c r="D517" s="10" t="inlineStr">
+        <is>
+          <t>Dwelling Type - Other</t>
+        </is>
+      </c>
+      <c r="E517" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F517" s="10" t="inlineStr">
+        <is>
+          <t>TextInput</t>
+        </is>
+      </c>
+      <c r="G517" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H517" s="10" t="inlineStr"/>
+      <c r="I517" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J517" s="10" t="inlineStr"/>
+      <c r="K517" s="10" t="inlineStr"/>
+      <c r="L517" s="10" t="inlineStr"/>
+      <c r="M517" s="10" t="inlineStr"/>
+      <c r="N517" s="10" t="inlineStr"/>
+      <c r="O517" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P517" s="10" t="inlineStr"/>
+      <c r="Q517" s="10" t="inlineStr"/>
+      <c r="R517" s="10" t="inlineStr"/>
+      <c r="S517" s="10" t="inlineStr"/>
+      <c r="T517" s="10" t="inlineStr"/>
+      <c r="U517" s="10" t="inlineStr"/>
+    </row>
+    <row r="518" ht="22" customHeight="1">
+      <c r="A518" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::WhenWasYourHomeBuilt</t>
+        </is>
+      </c>
+      <c r="B518" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C518" s="10" t="inlineStr">
+        <is>
+          <t>WhenWasYourHomeBuilt</t>
+        </is>
+      </c>
+      <c r="D518" s="10" t="inlineStr">
+        <is>
+          <t>When was your home built?</t>
+        </is>
+      </c>
+      <c r="E518" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F518" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G518" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H518" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I518" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J518" s="10" t="inlineStr"/>
+      <c r="K518" s="10" t="inlineStr"/>
+      <c r="L518" s="10" t="inlineStr"/>
+      <c r="M518" s="10" t="inlineStr"/>
+      <c r="N518" s="10" t="inlineStr"/>
+      <c r="O518" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P518" s="10" t="inlineStr"/>
+      <c r="Q518" s="10" t="inlineStr"/>
+      <c r="R518" s="10" t="inlineStr"/>
+      <c r="S518" s="10" t="inlineStr"/>
+      <c r="T518" s="10" t="inlineStr"/>
+      <c r="U518" s="10" t="inlineStr"/>
+    </row>
+    <row r="519" ht="22" customHeight="1">
+      <c r="A519" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowLargeIsYourHome</t>
+        </is>
+      </c>
+      <c r="B519" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C519" s="10" t="inlineStr">
+        <is>
+          <t>HowLargeIsYourHome</t>
+        </is>
+      </c>
+      <c r="D519" s="10" t="inlineStr">
+        <is>
+          <t>How large is your home?</t>
+        </is>
+      </c>
+      <c r="E519" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F519" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G519" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H519" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I519" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J519" s="10" t="inlineStr"/>
+      <c r="K519" s="10" t="inlineStr"/>
+      <c r="L519" s="10" t="inlineStr"/>
+      <c r="M519" s="10" t="inlineStr"/>
+      <c r="N519" s="10" t="inlineStr"/>
+      <c r="O519" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P519" s="10" t="inlineStr"/>
+      <c r="Q519" s="10" t="inlineStr"/>
+      <c r="R519" s="10" t="inlineStr"/>
+      <c r="S519" s="10" t="inlineStr"/>
+      <c r="T519" s="10" t="inlineStr"/>
+      <c r="U519" s="10" t="inlineStr"/>
+    </row>
+    <row r="520" ht="22" customHeight="1">
+      <c r="A520" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::HowOldAreYou</t>
+        </is>
+      </c>
+      <c r="B520" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C520" s="10" t="inlineStr">
+        <is>
+          <t>HowOldAreYou</t>
+        </is>
+      </c>
+      <c r="D520" s="10" t="inlineStr">
+        <is>
+          <t>How old are you?</t>
+        </is>
+      </c>
+      <c r="E520" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F520" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G520" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H520" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I520" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J520" s="10" t="inlineStr"/>
+      <c r="K520" s="10" t="inlineStr"/>
+      <c r="L520" s="10" t="inlineStr"/>
+      <c r="M520" s="10" t="inlineStr"/>
+      <c r="N520" s="10" t="inlineStr"/>
+      <c r="O520" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P520" s="10" t="inlineStr"/>
+      <c r="Q520" s="10" t="inlineStr"/>
+      <c r="R520" s="10" t="inlineStr"/>
+      <c r="S520" s="10" t="inlineStr"/>
+      <c r="T520" s="10" t="inlineStr"/>
+      <c r="U520" s="10" t="inlineStr"/>
+    </row>
+    <row r="521" ht="22" customHeight="1">
+      <c r="A521" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::IncludingYourselfHowManyPeopleAreLivingInYourHousehold</t>
+        </is>
+      </c>
+      <c r="B521" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C521" s="10" t="inlineStr">
+        <is>
+          <t>IncludingYourselfHowManyPeopleAreLivingInYourHousehold</t>
+        </is>
+      </c>
+      <c r="D521" s="10" t="inlineStr">
+        <is>
+          <t>Including yourself, how many people are living in your household?</t>
+        </is>
+      </c>
+      <c r="E521" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F521" s="10" t="inlineStr">
+        <is>
+          <t>NumberInput</t>
+        </is>
+      </c>
+      <c r="G521" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H521" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I521" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J521" s="10" t="inlineStr"/>
+      <c r="K521" s="10" t="inlineStr"/>
+      <c r="L521" s="10" t="inlineStr"/>
+      <c r="M521" s="10" t="inlineStr"/>
+      <c r="N521" s="10" t="inlineStr"/>
+      <c r="O521" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P521" s="10" t="inlineStr"/>
+      <c r="Q521" s="10" t="inlineStr"/>
+      <c r="R521" s="10" t="inlineStr"/>
+      <c r="S521" s="10" t="inlineStr"/>
+      <c r="T521" s="10" t="inlineStr"/>
+      <c r="U521" s="10" t="inlineStr"/>
+    </row>
+    <row r="522" ht="22" customHeight="1">
+      <c r="A522" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::IncomeAmountBasedonHouseholdSize</t>
+        </is>
+      </c>
+      <c r="B522" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C522" s="10" t="inlineStr">
+        <is>
+          <t>IncomeAmountBasedonHouseholdSize</t>
+        </is>
+      </c>
+      <c r="D522" s="10" t="inlineStr">
+        <is>
+          <t>Income Amount Based on Household Size</t>
+        </is>
+      </c>
+      <c r="E522" s="10" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="F522" s="10" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="G522" s="10" t="inlineStr"/>
+      <c r="H522" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I522" s="10" t="inlineStr"/>
+      <c r="J522" s="10" t="inlineStr"/>
+      <c r="K522" s="10" t="inlineStr"/>
+      <c r="L522" s="10" t="inlineStr"/>
+      <c r="M522" s="10" t="inlineStr"/>
+      <c r="N522" s="10" t="inlineStr"/>
+      <c r="O522" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P522" s="10" t="inlineStr">
+        <is>
+          <t>const SetValue = async (context) =&gt; { // Household size thresholds mapped to income limits const incomeThresholds = { 1: "$25,750", 2: "$34,840", 3: "$43,920", 4: "$53,000", 5: "$62,080", 6: "$71,160", 7: "$80,240", 8: "$89,320", 9: "$98,400", 10: "$107,480", 11: "$116,560", "12+": "$125,640" }; // Extract household size const householdSize = parseFloat(context?.Form?.DemographicsPage?.IncludingYourselfHowManyPeopleAreLivingInYourHousehold?.Value) || 0; // Handle household sizes up to 11, and 12</t>
+        </is>
+      </c>
+      <c r="Q522" s="10" t="inlineStr"/>
+      <c r="R522" s="10" t="inlineStr"/>
+      <c r="S522" s="10" t="inlineStr"/>
+      <c r="T522" s="10" t="inlineStr"/>
+      <c r="U522" s="10" t="inlineStr">
+        <is>
+          <t>IncludingYourselfHowManyPeopleAreLivingInYourHousehold</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="22" customHeight="1">
+      <c r="A523" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey::IsYourAnnualHouseholdIncomeOverOrUnderBasedOnTheHouseholdSize</t>
+        </is>
+      </c>
+      <c r="B523" s="10" t="inlineStr">
+        <is>
+          <t>QAR Survey</t>
+        </is>
+      </c>
+      <c r="C523" s="10" t="inlineStr">
+        <is>
+          <t>IsYourAnnualHouseholdIncomeOverOrUnderBasedOnTheHouseholdSize</t>
+        </is>
+      </c>
+      <c r="D523" s="10" t="inlineStr">
+        <is>
+          <t>Is your annual household income over or under based on the household size?</t>
+        </is>
+      </c>
+      <c r="E523" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F523" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G523" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H523" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I523" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J523" s="10" t="inlineStr"/>
+      <c r="K523" s="10" t="inlineStr"/>
+      <c r="L523" s="10" t="inlineStr"/>
+      <c r="M523" s="10" t="inlineStr"/>
+      <c r="N523" s="10" t="inlineStr"/>
+      <c r="O523" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P523" s="10" t="inlineStr"/>
+      <c r="Q523" s="10" t="inlineStr"/>
+      <c r="R523" s="10" t="inlineStr"/>
+      <c r="S523" s="10" t="inlineStr"/>
+      <c r="T523" s="10" t="inlineStr"/>
+      <c r="U523" s="10" t="inlineStr"/>
+    </row>
+    <row r="524" ht="22" customHeight="1">
+      <c r="A524" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::EmployeeName</t>
+        </is>
+      </c>
+      <c r="B524" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C524" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeName</t>
+        </is>
+      </c>
+      <c r="D524" s="10" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="E524" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F524" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeSelect</t>
+        </is>
+      </c>
+      <c r="G524" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H524" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I524" s="10" t="inlineStr"/>
+      <c r="J524" s="10" t="inlineStr"/>
+      <c r="K524" s="10" t="inlineStr"/>
+      <c r="L524" s="10" t="inlineStr"/>
+      <c r="M524" s="10" t="inlineStr"/>
+      <c r="N524" s="10" t="inlineStr"/>
+      <c r="O524" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P524" s="10" t="inlineStr"/>
+      <c r="Q524" s="10" t="inlineStr"/>
+      <c r="R524" s="10" t="inlineStr"/>
+      <c r="S524" s="10" t="inlineStr"/>
+      <c r="T524" s="10" t="inlineStr"/>
+      <c r="U524" s="10" t="inlineStr"/>
+    </row>
+    <row r="525" ht="22" customHeight="1">
+      <c r="A525" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::EmployeeName2</t>
+        </is>
+      </c>
+      <c r="B525" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C525" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeName2</t>
+        </is>
+      </c>
+      <c r="D525" s="10" t="inlineStr">
+        <is>
+          <t>Partner Name</t>
+        </is>
+      </c>
+      <c r="E525" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F525" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeSelect</t>
+        </is>
+      </c>
+      <c r="G525" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H525" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I525" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J525" s="10" t="inlineStr"/>
+      <c r="K525" s="10" t="inlineStr"/>
+      <c r="L525" s="10" t="inlineStr"/>
+      <c r="M525" s="10" t="inlineStr"/>
+      <c r="N525" s="10" t="inlineStr"/>
+      <c r="O525" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P525" s="10" t="inlineStr"/>
+      <c r="Q525" s="10" t="inlineStr"/>
+      <c r="R525" s="10" t="inlineStr"/>
+      <c r="S525" s="10" t="inlineStr"/>
+      <c r="T525" s="10" t="inlineStr"/>
+      <c r="U525" s="10" t="inlineStr"/>
+    </row>
+    <row r="526" ht="22" customHeight="1">
+      <c r="A526" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::EmployeeEmail</t>
+        </is>
+      </c>
+      <c r="B526" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C526" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeEmail</t>
+        </is>
+      </c>
+      <c r="D526" s="10" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E526" s="10" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="F526" s="10" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="G526" s="10" t="inlineStr"/>
+      <c r="H526" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I526" s="10" t="inlineStr"/>
+      <c r="J526" s="10" t="inlineStr"/>
+      <c r="K526" s="10" t="inlineStr"/>
+      <c r="L526" s="10" t="inlineStr"/>
+      <c r="M526" s="10" t="inlineStr"/>
+      <c r="N526" s="10" t="inlineStr"/>
+      <c r="O526" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P526" s="10" t="inlineStr">
+        <is>
+          <t>const SetValue = async (context) =&gt; { //Code Here return context?.Form?.EmployeeInformationPage?.EmployeeName?.EmployeeEmailAddress; }</t>
+        </is>
+      </c>
+      <c r="Q526" s="10" t="inlineStr"/>
+      <c r="R526" s="10" t="inlineStr"/>
+      <c r="S526" s="10" t="inlineStr"/>
+      <c r="T526" s="10" t="inlineStr"/>
+      <c r="U526" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeName</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="22" customHeight="1">
+      <c r="A527" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::EmployeeEmail2</t>
+        </is>
+      </c>
+      <c r="B527" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C527" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeEmail2</t>
+        </is>
+      </c>
+      <c r="D527" s="10" t="inlineStr">
+        <is>
+          <t>Partner Email</t>
+        </is>
+      </c>
+      <c r="E527" s="10" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="F527" s="10" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="G527" s="10" t="inlineStr"/>
+      <c r="H527" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I527" s="10" t="inlineStr"/>
+      <c r="J527" s="10" t="inlineStr"/>
+      <c r="K527" s="10" t="inlineStr"/>
+      <c r="L527" s="10" t="inlineStr"/>
+      <c r="M527" s="10" t="inlineStr"/>
+      <c r="N527" s="10" t="inlineStr"/>
+      <c r="O527" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P527" s="10" t="inlineStr">
+        <is>
+          <t>const SetValue = async (context) =&gt; { //Code Here return context?.Form?.EmployeeInformationPage?.EmployeeName2?.EmployeeEmailAddress; }</t>
+        </is>
+      </c>
+      <c r="Q527" s="10" t="inlineStr"/>
+      <c r="R527" s="10" t="inlineStr"/>
+      <c r="S527" s="10" t="inlineStr"/>
+      <c r="T527" s="10" t="inlineStr"/>
+      <c r="U527" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeName2</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="22" customHeight="1">
+      <c r="A528" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::Date</t>
+        </is>
+      </c>
+      <c r="B528" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C528" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D528" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E528" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F528" s="10" t="inlineStr">
+        <is>
+          <t>DateInput</t>
+        </is>
+      </c>
+      <c r="G528" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H528" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I528" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J528" s="10" t="inlineStr"/>
+      <c r="K528" s="10" t="inlineStr"/>
+      <c r="L528" s="10" t="inlineStr"/>
+      <c r="M528" s="10" t="inlineStr"/>
+      <c r="N528" s="10" t="inlineStr"/>
+      <c r="O528" s="10" t="inlineStr">
+        <is>
+          <t>DateValidator</t>
+        </is>
+      </c>
+      <c r="P528" s="10" t="inlineStr"/>
+      <c r="Q528" s="10" t="inlineStr"/>
+      <c r="R528" s="10" t="inlineStr"/>
+      <c r="S528" s="10" t="inlineStr"/>
+      <c r="T528" s="10" t="inlineStr"/>
+      <c r="U528" s="10" t="inlineStr"/>
+    </row>
+    <row r="529" ht="22" customHeight="1">
+      <c r="A529" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::VehicleNumber</t>
+        </is>
+      </c>
+      <c r="B529" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C529" s="10" t="inlineStr">
+        <is>
+          <t>VehicleNumber</t>
+        </is>
+      </c>
+      <c r="D529" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Number</t>
+        </is>
+      </c>
+      <c r="E529" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F529" s="10" t="inlineStr">
+        <is>
+          <t>DropDownInput</t>
+        </is>
+      </c>
+      <c r="G529" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H529" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I529" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J529" s="10" t="inlineStr"/>
+      <c r="K529" s="10" t="inlineStr"/>
+      <c r="L529" s="10" t="inlineStr"/>
+      <c r="M529" s="10" t="inlineStr"/>
+      <c r="N529" s="10" t="inlineStr"/>
+      <c r="O529" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P529" s="10" t="inlineStr"/>
+      <c r="Q529" s="10" t="inlineStr"/>
+      <c r="R529" s="10" t="inlineStr"/>
+      <c r="S529" s="10" t="inlineStr"/>
+      <c r="T529" s="10" t="inlineStr"/>
+      <c r="U529" s="10" t="inlineStr"/>
+    </row>
+    <row r="530" ht="22" customHeight="1">
+      <c r="A530" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::OdometerReading</t>
+        </is>
+      </c>
+      <c r="B530" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C530" s="10" t="inlineStr">
+        <is>
+          <t>OdometerReading</t>
+        </is>
+      </c>
+      <c r="D530" s="10" t="inlineStr">
+        <is>
+          <t>Odometer Reading</t>
+        </is>
+      </c>
+      <c r="E530" s="10" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F530" s="10" t="inlineStr">
+        <is>
+          <t>NumberInput</t>
+        </is>
+      </c>
+      <c r="G530" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H530" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I530" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J530" s="10" t="inlineStr"/>
+      <c r="K530" s="10" t="inlineStr"/>
+      <c r="L530" s="10" t="inlineStr"/>
+      <c r="M530" s="10" t="inlineStr"/>
+      <c r="N530" s="10" t="inlineStr"/>
+      <c r="O530" s="10" t="inlineStr">
+        <is>
+          <t>NumberValidator</t>
+        </is>
+      </c>
+      <c r="P530" s="10" t="inlineStr"/>
+      <c r="Q530" s="10" t="inlineStr"/>
+      <c r="R530" s="10" t="inlineStr"/>
+      <c r="S530" s="10" t="inlineStr"/>
+      <c r="T530" s="10" t="inlineStr"/>
+      <c r="U530" s="10" t="inlineStr"/>
+    </row>
+    <row r="531" ht="22" customHeight="1">
+      <c r="A531" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsFireExtinguisherCharged</t>
+        </is>
+      </c>
+      <c r="B531" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C531" s="10" t="inlineStr">
+        <is>
+          <t>IsFireExtinguisherCharged</t>
+        </is>
+      </c>
+      <c r="D531" s="10" t="inlineStr">
+        <is>
+          <t>Is fire extinguisher charged?</t>
+        </is>
+      </c>
+      <c r="E531" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F531" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G531" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H531" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I531" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J531" s="10" t="inlineStr"/>
+      <c r="K531" s="10" t="inlineStr"/>
+      <c r="L531" s="10" t="inlineStr"/>
+      <c r="M531" s="10" t="inlineStr"/>
+      <c r="N531" s="10" t="inlineStr"/>
+      <c r="O531" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P531" s="10" t="inlineStr"/>
+      <c r="Q531" s="10" t="inlineStr"/>
+      <c r="R531" s="10" t="inlineStr"/>
+      <c r="S531" s="10" t="inlineStr"/>
+      <c r="T531" s="10" t="inlineStr"/>
+      <c r="U531" s="10" t="inlineStr"/>
+    </row>
+    <row r="532" ht="22" customHeight="1">
+      <c r="A532" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheVehicleExteriorFreeOfVisibleDamage</t>
+        </is>
+      </c>
+      <c r="B532" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C532" s="10" t="inlineStr">
+        <is>
+          <t>IsTheVehicleExteriorFreeOfVisibleDamage</t>
+        </is>
+      </c>
+      <c r="D532" s="10" t="inlineStr">
+        <is>
+          <t>Is the vehicle exterior free of visible damage?</t>
+        </is>
+      </c>
+      <c r="E532" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F532" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G532" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H532" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I532" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J532" s="10" t="inlineStr"/>
+      <c r="K532" s="10" t="inlineStr"/>
+      <c r="L532" s="10" t="inlineStr"/>
+      <c r="M532" s="10" t="inlineStr"/>
+      <c r="N532" s="10" t="inlineStr"/>
+      <c r="O532" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P532" s="10" t="inlineStr"/>
+      <c r="Q532" s="10" t="inlineStr"/>
+      <c r="R532" s="10" t="inlineStr"/>
+      <c r="S532" s="10" t="inlineStr"/>
+      <c r="T532" s="10" t="inlineStr"/>
+      <c r="U532" s="10" t="inlineStr"/>
+    </row>
+    <row r="533" ht="22" customHeight="1">
+      <c r="A533" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheVehicleCleanInAppearance</t>
+        </is>
+      </c>
+      <c r="B533" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C533" s="10" t="inlineStr">
+        <is>
+          <t>IsTheVehicleCleanInAppearance</t>
+        </is>
+      </c>
+      <c r="D533" s="10" t="inlineStr">
+        <is>
+          <t>Is the vehicle clean in appearance?</t>
+        </is>
+      </c>
+      <c r="E533" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F533" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G533" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H533" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I533" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J533" s="10" t="inlineStr"/>
+      <c r="K533" s="10" t="inlineStr"/>
+      <c r="L533" s="10" t="inlineStr"/>
+      <c r="M533" s="10" t="inlineStr"/>
+      <c r="N533" s="10" t="inlineStr"/>
+      <c r="O533" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P533" s="10" t="inlineStr"/>
+      <c r="Q533" s="10" t="inlineStr"/>
+      <c r="R533" s="10" t="inlineStr"/>
+      <c r="S533" s="10" t="inlineStr"/>
+      <c r="T533" s="10" t="inlineStr"/>
+      <c r="U533" s="10" t="inlineStr"/>
+    </row>
+    <row r="534" ht="22" customHeight="1">
+      <c r="A534" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreThereAnySignsOfFluidLeakageUnderneathVehicle</t>
+        </is>
+      </c>
+      <c r="B534" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C534" s="10" t="inlineStr">
+        <is>
+          <t>AreThereAnySignsOfFluidLeakageUnderneathVehicle</t>
+        </is>
+      </c>
+      <c r="D534" s="10" t="inlineStr">
+        <is>
+          <t>Are there any signs of fluid leakage underneath vehicle?</t>
+        </is>
+      </c>
+      <c r="E534" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F534" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G534" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H534" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I534" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J534" s="10" t="inlineStr"/>
+      <c r="K534" s="10" t="inlineStr"/>
+      <c r="L534" s="10" t="inlineStr"/>
+      <c r="M534" s="10" t="inlineStr"/>
+      <c r="N534" s="10" t="inlineStr"/>
+      <c r="O534" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P534" s="10" t="inlineStr"/>
+      <c r="Q534" s="10" t="inlineStr"/>
+      <c r="R534" s="10" t="inlineStr"/>
+      <c r="S534" s="10" t="inlineStr"/>
+      <c r="T534" s="10" t="inlineStr"/>
+      <c r="U534" s="10" t="inlineStr"/>
+    </row>
+    <row r="535" ht="22" customHeight="1">
+      <c r="A535" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreAllTiresInGoodCondition</t>
+        </is>
+      </c>
+      <c r="B535" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C535" s="10" t="inlineStr">
+        <is>
+          <t>AreAllTiresInGoodCondition</t>
+        </is>
+      </c>
+      <c r="D535" s="10" t="inlineStr">
+        <is>
+          <t>Are all tires in good condition?</t>
+        </is>
+      </c>
+      <c r="E535" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F535" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G535" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H535" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I535" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J535" s="10" t="inlineStr"/>
+      <c r="K535" s="10" t="inlineStr"/>
+      <c r="L535" s="10" t="inlineStr"/>
+      <c r="M535" s="10" t="inlineStr"/>
+      <c r="N535" s="10" t="inlineStr"/>
+      <c r="O535" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P535" s="10" t="inlineStr"/>
+      <c r="Q535" s="10" t="inlineStr"/>
+      <c r="R535" s="10" t="inlineStr"/>
+      <c r="S535" s="10" t="inlineStr"/>
+      <c r="T535" s="10" t="inlineStr"/>
+      <c r="U535" s="10" t="inlineStr"/>
+    </row>
+    <row r="536" ht="22" customHeight="1">
+      <c r="A536" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::LeakageUnderneathVehiclePhoto</t>
+        </is>
+      </c>
+      <c r="B536" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C536" s="10" t="inlineStr">
+        <is>
+          <t>LeakageUnderneathVehiclePhoto</t>
+        </is>
+      </c>
+      <c r="D536" s="10" t="inlineStr">
+        <is>
+          <t>Leakage Underneath Vehicle Photo</t>
+        </is>
+      </c>
+      <c r="E536" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F536" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G536" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H536" s="10" t="inlineStr"/>
+      <c r="I536" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J536" s="10" t="inlineStr"/>
+      <c r="K536" s="10" t="inlineStr"/>
+      <c r="L536" s="10" t="inlineStr"/>
+      <c r="M536" s="10" t="inlineStr"/>
+      <c r="N536" s="10" t="inlineStr"/>
+      <c r="O536" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P536" s="10" t="inlineStr"/>
+      <c r="Q536" s="10" t="inlineStr"/>
+      <c r="R536" s="10" t="inlineStr"/>
+      <c r="S536" s="10" t="inlineStr"/>
+      <c r="T536" s="10" t="inlineStr"/>
+      <c r="U536" s="10" t="inlineStr"/>
+    </row>
+    <row r="537" ht="22" customHeight="1">
+      <c r="A537" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::TirePhotos</t>
+        </is>
+      </c>
+      <c r="B537" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C537" s="10" t="inlineStr">
+        <is>
+          <t>TirePhotos</t>
+        </is>
+      </c>
+      <c r="D537" s="10" t="inlineStr">
+        <is>
+          <t>Tire Photos</t>
+        </is>
+      </c>
+      <c r="E537" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F537" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G537" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H537" s="10" t="inlineStr"/>
+      <c r="I537" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J537" s="10" t="inlineStr"/>
+      <c r="K537" s="10" t="inlineStr"/>
+      <c r="L537" s="10" t="inlineStr"/>
+      <c r="M537" s="10" t="inlineStr"/>
+      <c r="N537" s="10" t="inlineStr"/>
+      <c r="O537" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P537" s="10" t="inlineStr"/>
+      <c r="Q537" s="10" t="inlineStr"/>
+      <c r="R537" s="10" t="inlineStr"/>
+      <c r="S537" s="10" t="inlineStr"/>
+      <c r="T537" s="10" t="inlineStr"/>
+      <c r="U537" s="10" t="inlineStr"/>
+    </row>
+    <row r="538" ht="22" customHeight="1">
+      <c r="A538" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::VisibleDamageNotes</t>
+        </is>
+      </c>
+      <c r="B538" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C538" s="10" t="inlineStr">
+        <is>
+          <t>VisibleDamageNotes</t>
+        </is>
+      </c>
+      <c r="D538" s="10" t="inlineStr">
+        <is>
+          <t>Visible Damage Notes</t>
+        </is>
+      </c>
+      <c r="E538" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F538" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G538" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H538" s="10" t="inlineStr"/>
+      <c r="I538" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J538" s="10" t="inlineStr"/>
+      <c r="K538" s="10" t="inlineStr"/>
+      <c r="L538" s="10" t="inlineStr"/>
+      <c r="M538" s="10" t="inlineStr"/>
+      <c r="N538" s="10" t="inlineStr"/>
+      <c r="O538" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P538" s="10" t="inlineStr"/>
+      <c r="Q538" s="10" t="inlineStr"/>
+      <c r="R538" s="10" t="inlineStr"/>
+      <c r="S538" s="10" t="inlineStr"/>
+      <c r="T538" s="10" t="inlineStr"/>
+      <c r="U538" s="10" t="inlineStr"/>
+    </row>
+    <row r="539" ht="22" customHeight="1">
+      <c r="A539" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::FireExtinguisherPhoto</t>
+        </is>
+      </c>
+      <c r="B539" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C539" s="10" t="inlineStr">
+        <is>
+          <t>FireExtinguisherPhoto</t>
+        </is>
+      </c>
+      <c r="D539" s="10" t="inlineStr">
+        <is>
+          <t>Fire Extinguisher Photo</t>
+        </is>
+      </c>
+      <c r="E539" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F539" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G539" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H539" s="10" t="inlineStr"/>
+      <c r="I539" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J539" s="10" t="inlineStr"/>
+      <c r="K539" s="10" t="inlineStr"/>
+      <c r="L539" s="10" t="inlineStr"/>
+      <c r="M539" s="10" t="inlineStr"/>
+      <c r="N539" s="10" t="inlineStr"/>
+      <c r="O539" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P539" s="10" t="inlineStr"/>
+      <c r="Q539" s="10" t="inlineStr"/>
+      <c r="R539" s="10" t="inlineStr"/>
+      <c r="S539" s="10" t="inlineStr"/>
+      <c r="T539" s="10" t="inlineStr"/>
+      <c r="U539" s="10" t="inlineStr"/>
+    </row>
+    <row r="540" ht="22" customHeight="1">
+      <c r="A540" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::VehicleAppearancePhoto</t>
+        </is>
+      </c>
+      <c r="B540" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C540" s="10" t="inlineStr">
+        <is>
+          <t>VehicleAppearancePhoto</t>
+        </is>
+      </c>
+      <c r="D540" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Appearance Photo</t>
+        </is>
+      </c>
+      <c r="E540" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F540" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G540" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H540" s="10" t="inlineStr"/>
+      <c r="I540" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J540" s="10" t="inlineStr"/>
+      <c r="K540" s="10" t="inlineStr"/>
+      <c r="L540" s="10" t="inlineStr"/>
+      <c r="M540" s="10" t="inlineStr"/>
+      <c r="N540" s="10" t="inlineStr"/>
+      <c r="O540" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P540" s="10" t="inlineStr"/>
+      <c r="Q540" s="10" t="inlineStr"/>
+      <c r="R540" s="10" t="inlineStr"/>
+      <c r="S540" s="10" t="inlineStr"/>
+      <c r="T540" s="10" t="inlineStr"/>
+      <c r="U540" s="10" t="inlineStr"/>
+    </row>
+    <row r="541" ht="22" customHeight="1">
+      <c r="A541" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::VisibleExteriorDamagePhoto</t>
+        </is>
+      </c>
+      <c r="B541" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C541" s="10" t="inlineStr">
+        <is>
+          <t>VisibleExteriorDamagePhoto</t>
+        </is>
+      </c>
+      <c r="D541" s="10" t="inlineStr">
+        <is>
+          <t>Visible Exterior Damage Photo</t>
+        </is>
+      </c>
+      <c r="E541" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F541" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G541" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H541" s="10" t="inlineStr"/>
+      <c r="I541" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J541" s="10" t="inlineStr"/>
+      <c r="K541" s="10" t="inlineStr"/>
+      <c r="L541" s="10" t="inlineStr"/>
+      <c r="M541" s="10" t="inlineStr"/>
+      <c r="N541" s="10" t="inlineStr"/>
+      <c r="O541" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P541" s="10" t="inlineStr"/>
+      <c r="Q541" s="10" t="inlineStr"/>
+      <c r="R541" s="10" t="inlineStr"/>
+      <c r="S541" s="10" t="inlineStr"/>
+      <c r="T541" s="10" t="inlineStr"/>
+      <c r="U541" s="10" t="inlineStr"/>
+    </row>
+    <row r="542" ht="22" customHeight="1">
+      <c r="A542" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreAllTiresProperlyInflated</t>
+        </is>
+      </c>
+      <c r="B542" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C542" s="10" t="inlineStr">
+        <is>
+          <t>AreAllTiresProperlyInflated</t>
+        </is>
+      </c>
+      <c r="D542" s="10" t="inlineStr">
+        <is>
+          <t>Are all tires properly inflated?</t>
+        </is>
+      </c>
+      <c r="E542" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F542" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G542" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H542" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I542" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J542" s="10" t="inlineStr"/>
+      <c r="K542" s="10" t="inlineStr"/>
+      <c r="L542" s="10" t="inlineStr"/>
+      <c r="M542" s="10" t="inlineStr"/>
+      <c r="N542" s="10" t="inlineStr"/>
+      <c r="O542" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P542" s="10" t="inlineStr"/>
+      <c r="Q542" s="10" t="inlineStr"/>
+      <c r="R542" s="10" t="inlineStr"/>
+      <c r="S542" s="10" t="inlineStr"/>
+      <c r="T542" s="10" t="inlineStr"/>
+      <c r="U542" s="10" t="inlineStr"/>
+    </row>
+    <row r="543" ht="22" customHeight="1">
+      <c r="A543" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::TirePressureVerifiedBy</t>
+        </is>
+      </c>
+      <c r="B543" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C543" s="10" t="inlineStr">
+        <is>
+          <t>TirePressureVerifiedBy</t>
+        </is>
+      </c>
+      <c r="D543" s="10" t="inlineStr">
+        <is>
+          <t>Tire Pressure Verified By?</t>
+        </is>
+      </c>
+      <c r="E543" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F543" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G543" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H543" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I543" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J543" s="10" t="inlineStr"/>
+      <c r="K543" s="10" t="inlineStr"/>
+      <c r="L543" s="10" t="inlineStr"/>
+      <c r="M543" s="10" t="inlineStr"/>
+      <c r="N543" s="10" t="inlineStr"/>
+      <c r="O543" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P543" s="10" t="inlineStr"/>
+      <c r="Q543" s="10" t="inlineStr"/>
+      <c r="R543" s="10" t="inlineStr"/>
+      <c r="S543" s="10" t="inlineStr"/>
+      <c r="T543" s="10" t="inlineStr"/>
+      <c r="U543" s="10" t="inlineStr"/>
+    </row>
+    <row r="544" ht="22" customHeight="1">
+      <c r="A544" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::ExteriorNotes</t>
+        </is>
+      </c>
+      <c r="B544" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C544" s="10" t="inlineStr">
+        <is>
+          <t>ExteriorNotes</t>
+        </is>
+      </c>
+      <c r="D544" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E544" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F544" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G544" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H544" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I544" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J544" s="10" t="inlineStr"/>
+      <c r="K544" s="10" t="inlineStr"/>
+      <c r="L544" s="10" t="inlineStr"/>
+      <c r="M544" s="10" t="inlineStr"/>
+      <c r="N544" s="10" t="inlineStr"/>
+      <c r="O544" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P544" s="10" t="inlineStr"/>
+      <c r="Q544" s="10" t="inlineStr"/>
+      <c r="R544" s="10" t="inlineStr"/>
+      <c r="S544" s="10" t="inlineStr"/>
+      <c r="T544" s="10" t="inlineStr"/>
+      <c r="U544" s="10" t="inlineStr"/>
+    </row>
+    <row r="545" ht="22" customHeight="1">
+      <c r="A545" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheInteriorOfVehicleFreeOfVisibleDamage</t>
+        </is>
+      </c>
+      <c r="B545" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C545" s="10" t="inlineStr">
+        <is>
+          <t>IsTheInteriorOfVehicleFreeOfVisibleDamage</t>
+        </is>
+      </c>
+      <c r="D545" s="10" t="inlineStr">
+        <is>
+          <t>Is the interior of vehicle free of visible damage?</t>
+        </is>
+      </c>
+      <c r="E545" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F545" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G545" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H545" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I545" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J545" s="10" t="inlineStr"/>
+      <c r="K545" s="10" t="inlineStr"/>
+      <c r="L545" s="10" t="inlineStr"/>
+      <c r="M545" s="10" t="inlineStr"/>
+      <c r="N545" s="10" t="inlineStr"/>
+      <c r="O545" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P545" s="10" t="inlineStr"/>
+      <c r="Q545" s="10" t="inlineStr"/>
+      <c r="R545" s="10" t="inlineStr"/>
+      <c r="S545" s="10" t="inlineStr"/>
+      <c r="T545" s="10" t="inlineStr"/>
+      <c r="U545" s="10" t="inlineStr"/>
+    </row>
+    <row r="546" ht="22" customHeight="1">
+      <c r="A546" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheVehicleSInteriorClean</t>
+        </is>
+      </c>
+      <c r="B546" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C546" s="10" t="inlineStr">
+        <is>
+          <t>IsTheVehicleSInteriorClean</t>
+        </is>
+      </c>
+      <c r="D546" s="10" t="inlineStr">
+        <is>
+          <t>Is the vehicle's interior clean?</t>
+        </is>
+      </c>
+      <c r="E546" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F546" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G546" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H546" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I546" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J546" s="10" t="inlineStr"/>
+      <c r="K546" s="10" t="inlineStr"/>
+      <c r="L546" s="10" t="inlineStr"/>
+      <c r="M546" s="10" t="inlineStr"/>
+      <c r="N546" s="10" t="inlineStr"/>
+      <c r="O546" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P546" s="10" t="inlineStr"/>
+      <c r="Q546" s="10" t="inlineStr"/>
+      <c r="R546" s="10" t="inlineStr"/>
+      <c r="S546" s="10" t="inlineStr"/>
+      <c r="T546" s="10" t="inlineStr"/>
+      <c r="U546" s="10" t="inlineStr"/>
+    </row>
+    <row r="547" ht="22" customHeight="1">
+      <c r="A547" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::VehicleInteriorDebrisPhoto</t>
+        </is>
+      </c>
+      <c r="B547" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C547" s="10" t="inlineStr">
+        <is>
+          <t>VehicleInteriorDebrisPhoto</t>
+        </is>
+      </c>
+      <c r="D547" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Interior Debris Photo</t>
+        </is>
+      </c>
+      <c r="E547" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F547" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G547" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H547" s="10" t="inlineStr"/>
+      <c r="I547" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J547" s="10" t="inlineStr"/>
+      <c r="K547" s="10" t="inlineStr"/>
+      <c r="L547" s="10" t="inlineStr"/>
+      <c r="M547" s="10" t="inlineStr"/>
+      <c r="N547" s="10" t="inlineStr"/>
+      <c r="O547" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P547" s="10" t="inlineStr"/>
+      <c r="Q547" s="10" t="inlineStr"/>
+      <c r="R547" s="10" t="inlineStr"/>
+      <c r="S547" s="10" t="inlineStr"/>
+      <c r="T547" s="10" t="inlineStr"/>
+      <c r="U547" s="10" t="inlineStr"/>
+    </row>
+    <row r="548" ht="22" customHeight="1">
+      <c r="A548" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::InteriorNotes</t>
+        </is>
+      </c>
+      <c r="B548" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C548" s="10" t="inlineStr">
+        <is>
+          <t>InteriorNotes</t>
+        </is>
+      </c>
+      <c r="D548" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E548" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F548" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G548" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H548" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I548" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J548" s="10" t="inlineStr"/>
+      <c r="K548" s="10" t="inlineStr"/>
+      <c r="L548" s="10" t="inlineStr"/>
+      <c r="M548" s="10" t="inlineStr"/>
+      <c r="N548" s="10" t="inlineStr"/>
+      <c r="O548" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P548" s="10" t="inlineStr"/>
+      <c r="Q548" s="10" t="inlineStr"/>
+      <c r="R548" s="10" t="inlineStr"/>
+      <c r="S548" s="10" t="inlineStr"/>
+      <c r="T548" s="10" t="inlineStr"/>
+      <c r="U548" s="10" t="inlineStr"/>
+    </row>
+    <row r="549" ht="22" customHeight="1">
+      <c r="A549" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::VehicleInteriorDamagePhoto</t>
+        </is>
+      </c>
+      <c r="B549" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C549" s="10" t="inlineStr">
+        <is>
+          <t>VehicleInteriorDamagePhoto</t>
+        </is>
+      </c>
+      <c r="D549" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Interior Damage Photo</t>
+        </is>
+      </c>
+      <c r="E549" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F549" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G549" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H549" s="10" t="inlineStr"/>
+      <c r="I549" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J549" s="10" t="inlineStr"/>
+      <c r="K549" s="10" t="inlineStr"/>
+      <c r="L549" s="10" t="inlineStr"/>
+      <c r="M549" s="10" t="inlineStr"/>
+      <c r="N549" s="10" t="inlineStr"/>
+      <c r="O549" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P549" s="10" t="inlineStr"/>
+      <c r="Q549" s="10" t="inlineStr"/>
+      <c r="R549" s="10" t="inlineStr"/>
+      <c r="S549" s="10" t="inlineStr"/>
+      <c r="T549" s="10" t="inlineStr"/>
+      <c r="U549" s="10" t="inlineStr"/>
+    </row>
+    <row r="550" ht="22" customHeight="1">
+      <c r="A550" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreSafetyBeltsWorkingProperly</t>
+        </is>
+      </c>
+      <c r="B550" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C550" s="10" t="inlineStr">
+        <is>
+          <t>AreSafetyBeltsWorkingProperly</t>
+        </is>
+      </c>
+      <c r="D550" s="10" t="inlineStr">
+        <is>
+          <t>Are safety belts working properly?</t>
+        </is>
+      </c>
+      <c r="E550" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F550" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G550" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H550" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I550" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J550" s="10" t="inlineStr"/>
+      <c r="K550" s="10" t="inlineStr"/>
+      <c r="L550" s="10" t="inlineStr"/>
+      <c r="M550" s="10" t="inlineStr"/>
+      <c r="N550" s="10" t="inlineStr"/>
+      <c r="O550" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P550" s="10" t="inlineStr"/>
+      <c r="Q550" s="10" t="inlineStr"/>
+      <c r="R550" s="10" t="inlineStr"/>
+      <c r="S550" s="10" t="inlineStr"/>
+      <c r="T550" s="10" t="inlineStr"/>
+      <c r="U550" s="10" t="inlineStr"/>
+    </row>
+    <row r="551" ht="22" customHeight="1">
+      <c r="A551" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsAFirstAidKitAvailable</t>
+        </is>
+      </c>
+      <c r="B551" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C551" s="10" t="inlineStr">
+        <is>
+          <t>IsAFirstAidKitAvailable</t>
+        </is>
+      </c>
+      <c r="D551" s="10" t="inlineStr">
+        <is>
+          <t>Is a first aid kit available?</t>
+        </is>
+      </c>
+      <c r="E551" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F551" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G551" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H551" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I551" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J551" s="10" t="inlineStr"/>
+      <c r="K551" s="10" t="inlineStr"/>
+      <c r="L551" s="10" t="inlineStr"/>
+      <c r="M551" s="10" t="inlineStr"/>
+      <c r="N551" s="10" t="inlineStr"/>
+      <c r="O551" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P551" s="10" t="inlineStr"/>
+      <c r="Q551" s="10" t="inlineStr"/>
+      <c r="R551" s="10" t="inlineStr"/>
+      <c r="S551" s="10" t="inlineStr"/>
+      <c r="T551" s="10" t="inlineStr"/>
+      <c r="U551" s="10" t="inlineStr"/>
+    </row>
+    <row r="552" ht="22" customHeight="1">
+      <c r="A552" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsAnEmergencyKitAvailable</t>
+        </is>
+      </c>
+      <c r="B552" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C552" s="10" t="inlineStr">
+        <is>
+          <t>IsAnEmergencyKitAvailable</t>
+        </is>
+      </c>
+      <c r="D552" s="10" t="inlineStr">
+        <is>
+          <t>Is an emergency kit available?</t>
+        </is>
+      </c>
+      <c r="E552" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F552" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G552" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H552" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I552" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J552" s="10" t="inlineStr"/>
+      <c r="K552" s="10" t="inlineStr"/>
+      <c r="L552" s="10" t="inlineStr"/>
+      <c r="M552" s="10" t="inlineStr"/>
+      <c r="N552" s="10" t="inlineStr"/>
+      <c r="O552" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P552" s="10" t="inlineStr"/>
+      <c r="Q552" s="10" t="inlineStr"/>
+      <c r="R552" s="10" t="inlineStr"/>
+      <c r="S552" s="10" t="inlineStr"/>
+      <c r="T552" s="10" t="inlineStr"/>
+      <c r="U552" s="10" t="inlineStr"/>
+    </row>
+    <row r="553" ht="22" customHeight="1">
+      <c r="A553" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheVehicleRegistrationAndInsuranceCardEasilyAccessible</t>
+        </is>
+      </c>
+      <c r="B553" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C553" s="10" t="inlineStr">
+        <is>
+          <t>IsTheVehicleRegistrationAndInsuranceCardEasilyAccessible</t>
+        </is>
+      </c>
+      <c r="D553" s="10" t="inlineStr">
+        <is>
+          <t>Is the vehicle registration and insurance card easily accessible?</t>
+        </is>
+      </c>
+      <c r="E553" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F553" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G553" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H553" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I553" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J553" s="10" t="inlineStr"/>
+      <c r="K553" s="10" t="inlineStr"/>
+      <c r="L553" s="10" t="inlineStr"/>
+      <c r="M553" s="10" t="inlineStr"/>
+      <c r="N553" s="10" t="inlineStr"/>
+      <c r="O553" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P553" s="10" t="inlineStr"/>
+      <c r="Q553" s="10" t="inlineStr"/>
+      <c r="R553" s="10" t="inlineStr"/>
+      <c r="S553" s="10" t="inlineStr"/>
+      <c r="T553" s="10" t="inlineStr"/>
+      <c r="U553" s="10" t="inlineStr"/>
+    </row>
+    <row r="554" ht="22" customHeight="1">
+      <c r="A554" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheVehicleSManualAvailable</t>
+        </is>
+      </c>
+      <c r="B554" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C554" s="10" t="inlineStr">
+        <is>
+          <t>IsTheVehicleSManualAvailable</t>
+        </is>
+      </c>
+      <c r="D554" s="10" t="inlineStr">
+        <is>
+          <t>Is the vehicle's manual available?</t>
+        </is>
+      </c>
+      <c r="E554" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F554" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G554" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H554" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I554" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J554" s="10" t="inlineStr"/>
+      <c r="K554" s="10" t="inlineStr"/>
+      <c r="L554" s="10" t="inlineStr"/>
+      <c r="M554" s="10" t="inlineStr"/>
+      <c r="N554" s="10" t="inlineStr"/>
+      <c r="O554" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P554" s="10" t="inlineStr"/>
+      <c r="Q554" s="10" t="inlineStr"/>
+      <c r="R554" s="10" t="inlineStr"/>
+      <c r="S554" s="10" t="inlineStr"/>
+      <c r="T554" s="10" t="inlineStr"/>
+      <c r="U554" s="10" t="inlineStr"/>
+    </row>
+    <row r="555" ht="22" customHeight="1">
+      <c r="A555" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTruckBinderAvailableIncludeHiipCodeOfSafePracticesInjuryIncidentFormAccidentReportingForm</t>
+        </is>
+      </c>
+      <c r="B555" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C555" s="10" t="inlineStr">
+        <is>
+          <t>IsTruckBinderAvailableIncludeHiipCodeOfSafePracticesInjuryIncidentFormAccidentReportingForm</t>
+        </is>
+      </c>
+      <c r="D555" s="10" t="inlineStr">
+        <is>
+          <t>Is truck binder available &amp; include HIIP, Code of Safe Practices, Injury/Incident Form, Accident Reporting Form?</t>
+        </is>
+      </c>
+      <c r="E555" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F555" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G555" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H555" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I555" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J555" s="10" t="inlineStr"/>
+      <c r="K555" s="10" t="inlineStr"/>
+      <c r="L555" s="10" t="inlineStr"/>
+      <c r="M555" s="10" t="inlineStr"/>
+      <c r="N555" s="10" t="inlineStr"/>
+      <c r="O555" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P555" s="10" t="inlineStr"/>
+      <c r="Q555" s="10" t="inlineStr"/>
+      <c r="R555" s="10" t="inlineStr"/>
+      <c r="S555" s="10" t="inlineStr"/>
+      <c r="T555" s="10" t="inlineStr"/>
+      <c r="U555" s="10" t="inlineStr"/>
+    </row>
+    <row r="556" ht="22" customHeight="1">
+      <c r="A556" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheHeadlightsWorking</t>
+        </is>
+      </c>
+      <c r="B556" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C556" s="10" t="inlineStr">
+        <is>
+          <t>AreTheHeadlightsWorking</t>
+        </is>
+      </c>
+      <c r="D556" s="10" t="inlineStr">
+        <is>
+          <t>Are the headlights working?</t>
+        </is>
+      </c>
+      <c r="E556" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F556" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G556" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H556" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I556" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J556" s="10" t="inlineStr"/>
+      <c r="K556" s="10" t="inlineStr"/>
+      <c r="L556" s="10" t="inlineStr"/>
+      <c r="M556" s="10" t="inlineStr"/>
+      <c r="N556" s="10" t="inlineStr"/>
+      <c r="O556" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P556" s="10" t="inlineStr"/>
+      <c r="Q556" s="10" t="inlineStr"/>
+      <c r="R556" s="10" t="inlineStr"/>
+      <c r="S556" s="10" t="inlineStr"/>
+      <c r="T556" s="10" t="inlineStr"/>
+      <c r="U556" s="10" t="inlineStr"/>
+    </row>
+    <row r="557" ht="22" customHeight="1">
+      <c r="A557" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheTaillightsWorking</t>
+        </is>
+      </c>
+      <c r="B557" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C557" s="10" t="inlineStr">
+        <is>
+          <t>AreTheTaillightsWorking</t>
+        </is>
+      </c>
+      <c r="D557" s="10" t="inlineStr">
+        <is>
+          <t>Are the taillights working?</t>
+        </is>
+      </c>
+      <c r="E557" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F557" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G557" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H557" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I557" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J557" s="10" t="inlineStr"/>
+      <c r="K557" s="10" t="inlineStr"/>
+      <c r="L557" s="10" t="inlineStr"/>
+      <c r="M557" s="10" t="inlineStr"/>
+      <c r="N557" s="10" t="inlineStr"/>
+      <c r="O557" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P557" s="10" t="inlineStr"/>
+      <c r="Q557" s="10" t="inlineStr"/>
+      <c r="R557" s="10" t="inlineStr"/>
+      <c r="S557" s="10" t="inlineStr"/>
+      <c r="T557" s="10" t="inlineStr"/>
+      <c r="U557" s="10" t="inlineStr"/>
+    </row>
+    <row r="558" ht="22" customHeight="1">
+      <c r="A558" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::OperationNotes</t>
+        </is>
+      </c>
+      <c r="B558" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C558" s="10" t="inlineStr">
+        <is>
+          <t>OperationNotes</t>
+        </is>
+      </c>
+      <c r="D558" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E558" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F558" s="10" t="inlineStr">
+        <is>
+          <t>TextAreaInput</t>
+        </is>
+      </c>
+      <c r="G558" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H558" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I558" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J558" s="10" t="inlineStr"/>
+      <c r="K558" s="10" t="inlineStr"/>
+      <c r="L558" s="10" t="inlineStr"/>
+      <c r="M558" s="10" t="inlineStr"/>
+      <c r="N558" s="10" t="inlineStr"/>
+      <c r="O558" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P558" s="10" t="inlineStr"/>
+      <c r="Q558" s="10" t="inlineStr"/>
+      <c r="R558" s="10" t="inlineStr"/>
+      <c r="S558" s="10" t="inlineStr"/>
+      <c r="T558" s="10" t="inlineStr"/>
+      <c r="U558" s="10" t="inlineStr"/>
+    </row>
+    <row r="559" ht="22" customHeight="1">
+      <c r="A559" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheBrakeLightsWorking</t>
+        </is>
+      </c>
+      <c r="B559" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C559" s="10" t="inlineStr">
+        <is>
+          <t>AreTheBrakeLightsWorking</t>
+        </is>
+      </c>
+      <c r="D559" s="10" t="inlineStr">
+        <is>
+          <t>Are the brake lights working?</t>
+        </is>
+      </c>
+      <c r="E559" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F559" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G559" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H559" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I559" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J559" s="10" t="inlineStr"/>
+      <c r="K559" s="10" t="inlineStr"/>
+      <c r="L559" s="10" t="inlineStr"/>
+      <c r="M559" s="10" t="inlineStr"/>
+      <c r="N559" s="10" t="inlineStr"/>
+      <c r="O559" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P559" s="10" t="inlineStr"/>
+      <c r="Q559" s="10" t="inlineStr"/>
+      <c r="R559" s="10" t="inlineStr"/>
+      <c r="S559" s="10" t="inlineStr"/>
+      <c r="T559" s="10" t="inlineStr"/>
+      <c r="U559" s="10" t="inlineStr"/>
+    </row>
+    <row r="560" ht="22" customHeight="1">
+      <c r="A560" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheBackUpLightsWorking</t>
+        </is>
+      </c>
+      <c r="B560" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C560" s="10" t="inlineStr">
+        <is>
+          <t>AreTheBackUpLightsWorking</t>
+        </is>
+      </c>
+      <c r="D560" s="10" t="inlineStr">
+        <is>
+          <t>Are the back-up lights working?</t>
+        </is>
+      </c>
+      <c r="E560" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F560" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G560" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H560" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I560" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J560" s="10" t="inlineStr"/>
+      <c r="K560" s="10" t="inlineStr"/>
+      <c r="L560" s="10" t="inlineStr"/>
+      <c r="M560" s="10" t="inlineStr"/>
+      <c r="N560" s="10" t="inlineStr"/>
+      <c r="O560" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P560" s="10" t="inlineStr"/>
+      <c r="Q560" s="10" t="inlineStr"/>
+      <c r="R560" s="10" t="inlineStr"/>
+      <c r="S560" s="10" t="inlineStr"/>
+      <c r="T560" s="10" t="inlineStr"/>
+      <c r="U560" s="10" t="inlineStr"/>
+    </row>
+    <row r="561" ht="22" customHeight="1">
+      <c r="A561" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheInteriorLightsWorking</t>
+        </is>
+      </c>
+      <c r="B561" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C561" s="10" t="inlineStr">
+        <is>
+          <t>AreTheInteriorLightsWorking</t>
+        </is>
+      </c>
+      <c r="D561" s="10" t="inlineStr">
+        <is>
+          <t>Are the interior lights working?</t>
+        </is>
+      </c>
+      <c r="E561" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F561" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G561" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H561" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I561" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J561" s="10" t="inlineStr"/>
+      <c r="K561" s="10" t="inlineStr"/>
+      <c r="L561" s="10" t="inlineStr"/>
+      <c r="M561" s="10" t="inlineStr"/>
+      <c r="N561" s="10" t="inlineStr"/>
+      <c r="O561" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P561" s="10" t="inlineStr"/>
+      <c r="Q561" s="10" t="inlineStr"/>
+      <c r="R561" s="10" t="inlineStr"/>
+      <c r="S561" s="10" t="inlineStr"/>
+      <c r="T561" s="10" t="inlineStr"/>
+      <c r="U561" s="10" t="inlineStr"/>
+    </row>
+    <row r="562" ht="22" customHeight="1">
+      <c r="A562" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheWindshieldWipersWorkingProperly</t>
+        </is>
+      </c>
+      <c r="B562" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C562" s="10" t="inlineStr">
+        <is>
+          <t>AreTheWindshieldWipersWorkingProperly</t>
+        </is>
+      </c>
+      <c r="D562" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Are the windshield wipers working properly? </t>
+        </is>
+      </c>
+      <c r="E562" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F562" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G562" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H562" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I562" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J562" s="10" t="inlineStr"/>
+      <c r="K562" s="10" t="inlineStr"/>
+      <c r="L562" s="10" t="inlineStr"/>
+      <c r="M562" s="10" t="inlineStr"/>
+      <c r="N562" s="10" t="inlineStr"/>
+      <c r="O562" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P562" s="10" t="inlineStr"/>
+      <c r="Q562" s="10" t="inlineStr"/>
+      <c r="R562" s="10" t="inlineStr"/>
+      <c r="S562" s="10" t="inlineStr"/>
+      <c r="T562" s="10" t="inlineStr"/>
+      <c r="U562" s="10" t="inlineStr"/>
+    </row>
+    <row r="563" ht="22" customHeight="1">
+      <c r="A563" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheWindshieldWiperBladesInGoodCondition</t>
+        </is>
+      </c>
+      <c r="B563" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C563" s="10" t="inlineStr">
+        <is>
+          <t>AreTheWindshieldWiperBladesInGoodCondition</t>
+        </is>
+      </c>
+      <c r="D563" s="10" t="inlineStr">
+        <is>
+          <t>Are the windshield wiper blades in good condition?</t>
+        </is>
+      </c>
+      <c r="E563" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F563" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G563" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H563" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I563" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J563" s="10" t="inlineStr"/>
+      <c r="K563" s="10" t="inlineStr"/>
+      <c r="L563" s="10" t="inlineStr"/>
+      <c r="M563" s="10" t="inlineStr"/>
+      <c r="N563" s="10" t="inlineStr"/>
+      <c r="O563" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P563" s="10" t="inlineStr"/>
+      <c r="Q563" s="10" t="inlineStr"/>
+      <c r="R563" s="10" t="inlineStr"/>
+      <c r="S563" s="10" t="inlineStr"/>
+      <c r="T563" s="10" t="inlineStr"/>
+      <c r="U563" s="10" t="inlineStr"/>
+    </row>
+    <row r="564" ht="22" customHeight="1">
+      <c r="A564" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheHornWorking</t>
+        </is>
+      </c>
+      <c r="B564" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C564" s="10" t="inlineStr">
+        <is>
+          <t>IsTheHornWorking</t>
+        </is>
+      </c>
+      <c r="D564" s="10" t="inlineStr">
+        <is>
+          <t>Is the horn working?</t>
+        </is>
+      </c>
+      <c r="E564" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F564" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G564" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H564" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I564" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J564" s="10" t="inlineStr"/>
+      <c r="K564" s="10" t="inlineStr"/>
+      <c r="L564" s="10" t="inlineStr"/>
+      <c r="M564" s="10" t="inlineStr"/>
+      <c r="N564" s="10" t="inlineStr"/>
+      <c r="O564" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P564" s="10" t="inlineStr"/>
+      <c r="Q564" s="10" t="inlineStr"/>
+      <c r="R564" s="10" t="inlineStr"/>
+      <c r="S564" s="10" t="inlineStr"/>
+      <c r="T564" s="10" t="inlineStr"/>
+      <c r="U564" s="10" t="inlineStr"/>
+    </row>
+    <row r="565" ht="22" customHeight="1">
+      <c r="A565" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AreTheProperMirrorsAvailableRearViewDriverPassenger</t>
+        </is>
+      </c>
+      <c r="B565" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C565" s="10" t="inlineStr">
+        <is>
+          <t>AreTheProperMirrorsAvailableRearViewDriverPassenger</t>
+        </is>
+      </c>
+      <c r="D565" s="10" t="inlineStr">
+        <is>
+          <t>Are the proper mirrors available? (Rear-view, Driver, Passenger)</t>
+        </is>
+      </c>
+      <c r="E565" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F565" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G565" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H565" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I565" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J565" s="10" t="inlineStr"/>
+      <c r="K565" s="10" t="inlineStr"/>
+      <c r="L565" s="10" t="inlineStr"/>
+      <c r="M565" s="10" t="inlineStr"/>
+      <c r="N565" s="10" t="inlineStr"/>
+      <c r="O565" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P565" s="10" t="inlineStr"/>
+      <c r="Q565" s="10" t="inlineStr"/>
+      <c r="R565" s="10" t="inlineStr"/>
+      <c r="S565" s="10" t="inlineStr"/>
+      <c r="T565" s="10" t="inlineStr"/>
+      <c r="U565" s="10" t="inlineStr"/>
+    </row>
+    <row r="566" ht="22" customHeight="1">
+      <c r="A566" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheParkingBrakeWorking</t>
+        </is>
+      </c>
+      <c r="B566" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C566" s="10" t="inlineStr">
+        <is>
+          <t>IsTheParkingBrakeWorking</t>
+        </is>
+      </c>
+      <c r="D566" s="10" t="inlineStr">
+        <is>
+          <t>Is the parking brake working?</t>
+        </is>
+      </c>
+      <c r="E566" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F566" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G566" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H566" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I566" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J566" s="10" t="inlineStr"/>
+      <c r="K566" s="10" t="inlineStr"/>
+      <c r="L566" s="10" t="inlineStr"/>
+      <c r="M566" s="10" t="inlineStr"/>
+      <c r="N566" s="10" t="inlineStr"/>
+      <c r="O566" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P566" s="10" t="inlineStr"/>
+      <c r="Q566" s="10" t="inlineStr"/>
+      <c r="R566" s="10" t="inlineStr"/>
+      <c r="S566" s="10" t="inlineStr"/>
+      <c r="T566" s="10" t="inlineStr"/>
+      <c r="U566" s="10" t="inlineStr"/>
+    </row>
+    <row r="567" ht="22" customHeight="1">
+      <c r="A567" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::DoTheTurnSignalsWork</t>
+        </is>
+      </c>
+      <c r="B567" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C567" s="10" t="inlineStr">
+        <is>
+          <t>DoTheTurnSignalsWork</t>
+        </is>
+      </c>
+      <c r="D567" s="10" t="inlineStr">
+        <is>
+          <t>Do the turn signals work?</t>
+        </is>
+      </c>
+      <c r="E567" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F567" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G567" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H567" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I567" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J567" s="10" t="inlineStr"/>
+      <c r="K567" s="10" t="inlineStr"/>
+      <c r="L567" s="10" t="inlineStr"/>
+      <c r="M567" s="10" t="inlineStr"/>
+      <c r="N567" s="10" t="inlineStr"/>
+      <c r="O567" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P567" s="10" t="inlineStr"/>
+      <c r="Q567" s="10" t="inlineStr"/>
+      <c r="R567" s="10" t="inlineStr"/>
+      <c r="S567" s="10" t="inlineStr"/>
+      <c r="T567" s="10" t="inlineStr"/>
+      <c r="U567" s="10" t="inlineStr"/>
+    </row>
+    <row r="568" ht="22" customHeight="1">
+      <c r="A568" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheSunVisorOperable</t>
+        </is>
+      </c>
+      <c r="B568" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C568" s="10" t="inlineStr">
+        <is>
+          <t>IsTheSunVisorOperable</t>
+        </is>
+      </c>
+      <c r="D568" s="10" t="inlineStr">
+        <is>
+          <t>Is the sun visor operable?</t>
+        </is>
+      </c>
+      <c r="E568" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F568" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G568" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H568" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I568" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J568" s="10" t="inlineStr"/>
+      <c r="K568" s="10" t="inlineStr"/>
+      <c r="L568" s="10" t="inlineStr"/>
+      <c r="M568" s="10" t="inlineStr"/>
+      <c r="N568" s="10" t="inlineStr"/>
+      <c r="O568" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P568" s="10" t="inlineStr"/>
+      <c r="Q568" s="10" t="inlineStr"/>
+      <c r="R568" s="10" t="inlineStr"/>
+      <c r="S568" s="10" t="inlineStr"/>
+      <c r="T568" s="10" t="inlineStr"/>
+      <c r="U568" s="10" t="inlineStr"/>
+    </row>
+    <row r="569" ht="22" customHeight="1">
+      <c r="A569" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::DoYouHaveYourSafetyCones</t>
+        </is>
+      </c>
+      <c r="B569" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C569" s="10" t="inlineStr">
+        <is>
+          <t>DoYouHaveYourSafetyCones</t>
+        </is>
+      </c>
+      <c r="D569" s="10" t="inlineStr">
+        <is>
+          <t>Do you have your safety cones?</t>
+        </is>
+      </c>
+      <c r="E569" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F569" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G569" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H569" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I569" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J569" s="10" t="inlineStr"/>
+      <c r="K569" s="10" t="inlineStr"/>
+      <c r="L569" s="10" t="inlineStr"/>
+      <c r="M569" s="10" t="inlineStr"/>
+      <c r="N569" s="10" t="inlineStr"/>
+      <c r="O569" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P569" s="10" t="inlineStr"/>
+      <c r="Q569" s="10" t="inlineStr"/>
+      <c r="R569" s="10" t="inlineStr"/>
+      <c r="S569" s="10" t="inlineStr"/>
+      <c r="T569" s="10" t="inlineStr"/>
+      <c r="U569" s="10" t="inlineStr"/>
+    </row>
+    <row r="570" ht="22" customHeight="1">
+      <c r="A570" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::DoesTheHeatingCoolingSystemWorkProperly</t>
+        </is>
+      </c>
+      <c r="B570" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C570" s="10" t="inlineStr">
+        <is>
+          <t>DoesTheHeatingCoolingSystemWorkProperly</t>
+        </is>
+      </c>
+      <c r="D570" s="10" t="inlineStr">
+        <is>
+          <t>Does the heating/cooling system work properly?</t>
+        </is>
+      </c>
+      <c r="E570" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F570" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G570" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H570" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I570" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J570" s="10" t="inlineStr"/>
+      <c r="K570" s="10" t="inlineStr"/>
+      <c r="L570" s="10" t="inlineStr"/>
+      <c r="M570" s="10" t="inlineStr"/>
+      <c r="N570" s="10" t="inlineStr"/>
+      <c r="O570" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P570" s="10" t="inlineStr"/>
+      <c r="Q570" s="10" t="inlineStr"/>
+      <c r="R570" s="10" t="inlineStr"/>
+      <c r="S570" s="10" t="inlineStr"/>
+      <c r="T570" s="10" t="inlineStr"/>
+      <c r="U570" s="10" t="inlineStr"/>
+    </row>
+    <row r="571" ht="22" customHeight="1">
+      <c r="A571" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsTheCheckEngineLightOn</t>
+        </is>
+      </c>
+      <c r="B571" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C571" s="10" t="inlineStr">
+        <is>
+          <t>IsTheCheckEngineLightOn</t>
+        </is>
+      </c>
+      <c r="D571" s="10" t="inlineStr">
+        <is>
+          <t>Is the check engine light on?</t>
+        </is>
+      </c>
+      <c r="E571" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F571" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G571" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H571" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I571" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J571" s="10" t="inlineStr"/>
+      <c r="K571" s="10" t="inlineStr"/>
+      <c r="L571" s="10" t="inlineStr"/>
+      <c r="M571" s="10" t="inlineStr"/>
+      <c r="N571" s="10" t="inlineStr"/>
+      <c r="O571" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P571" s="10" t="inlineStr"/>
+      <c r="Q571" s="10" t="inlineStr"/>
+      <c r="R571" s="10" t="inlineStr"/>
+      <c r="S571" s="10" t="inlineStr"/>
+      <c r="T571" s="10" t="inlineStr"/>
+      <c r="U571" s="10" t="inlineStr"/>
+    </row>
+    <row r="572" ht="22" customHeight="1">
+      <c r="A572" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::DoYouHaveSufficientGasInTheTankToCompleteYourRoute</t>
+        </is>
+      </c>
+      <c r="B572" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C572" s="10" t="inlineStr">
+        <is>
+          <t>DoYouHaveSufficientGasInTheTankToCompleteYourRoute</t>
+        </is>
+      </c>
+      <c r="D572" s="10" t="inlineStr">
+        <is>
+          <t>Do you have sufficient gas in the tank to complete your route?</t>
+        </is>
+      </c>
+      <c r="E572" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F572" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G572" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H572" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I572" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J572" s="10" t="inlineStr"/>
+      <c r="K572" s="10" t="inlineStr"/>
+      <c r="L572" s="10" t="inlineStr"/>
+      <c r="M572" s="10" t="inlineStr"/>
+      <c r="N572" s="10" t="inlineStr"/>
+      <c r="O572" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P572" s="10" t="inlineStr"/>
+      <c r="Q572" s="10" t="inlineStr"/>
+      <c r="R572" s="10" t="inlineStr"/>
+      <c r="S572" s="10" t="inlineStr"/>
+      <c r="T572" s="10" t="inlineStr"/>
+      <c r="U572" s="10" t="inlineStr"/>
+    </row>
+    <row r="573" ht="22" customHeight="1">
+      <c r="A573" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::PhotoOfFuelLevel</t>
+        </is>
+      </c>
+      <c r="B573" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C573" s="10" t="inlineStr">
+        <is>
+          <t>PhotoOfFuelLevel</t>
+        </is>
+      </c>
+      <c r="D573" s="10" t="inlineStr">
+        <is>
+          <t>Photo of Fuel Level</t>
+        </is>
+      </c>
+      <c r="E573" s="10" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F573" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G573" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H573" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I573" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J573" s="10" t="inlineStr"/>
+      <c r="K573" s="10" t="inlineStr"/>
+      <c r="L573" s="10" t="inlineStr"/>
+      <c r="M573" s="10" t="inlineStr"/>
+      <c r="N573" s="10" t="inlineStr"/>
+      <c r="O573" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P573" s="10" t="inlineStr"/>
+      <c r="Q573" s="10" t="inlineStr"/>
+      <c r="R573" s="10" t="inlineStr"/>
+      <c r="S573" s="10" t="inlineStr"/>
+      <c r="T573" s="10" t="inlineStr"/>
+      <c r="U573" s="10" t="inlineStr"/>
+    </row>
+    <row r="574" ht="22" customHeight="1">
+      <c r="A574" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::FuelUpNote</t>
+        </is>
+      </c>
+      <c r="B574" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C574" s="10" t="inlineStr">
+        <is>
+          <t>FuelUpNote</t>
+        </is>
+      </c>
+      <c r="D574" s="10" t="inlineStr"/>
+      <c r="E574" s="10" t="inlineStr"/>
+      <c r="F574" s="10" t="inlineStr">
+        <is>
+          <t>StaticText</t>
+        </is>
+      </c>
+      <c r="G574" s="10" t="inlineStr"/>
+      <c r="H574" s="10" t="inlineStr"/>
+      <c r="I574" s="10" t="inlineStr"/>
+      <c r="J574" s="10" t="inlineStr"/>
+      <c r="K574" s="10" t="inlineStr"/>
+      <c r="L574" s="10" t="inlineStr"/>
+      <c r="M574" s="10" t="inlineStr"/>
+      <c r="N574" s="10" t="inlineStr"/>
+      <c r="O574" s="10" t="inlineStr"/>
+      <c r="P574" s="10" t="inlineStr"/>
+      <c r="Q574" s="10" t="inlineStr"/>
+      <c r="R574" s="10" t="inlineStr"/>
+      <c r="S574" s="10" t="inlineStr"/>
+      <c r="T574" s="10" t="inlineStr"/>
+      <c r="U574" s="10" t="inlineStr"/>
+    </row>
+    <row r="575" ht="22" customHeight="1">
+      <c r="A575" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::IsYourPhoneConnectedToBluetooth</t>
+        </is>
+      </c>
+      <c r="B575" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C575" s="10" t="inlineStr">
+        <is>
+          <t>IsYourPhoneConnectedToBluetooth</t>
+        </is>
+      </c>
+      <c r="D575" s="10" t="inlineStr">
+        <is>
+          <t>Is your phone connected to bluetooth?</t>
+        </is>
+      </c>
+      <c r="E575" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F575" s="10" t="inlineStr">
+        <is>
+          <t>RadioInput</t>
+        </is>
+      </c>
+      <c r="G575" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H575" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I575" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J575" s="10" t="inlineStr"/>
+      <c r="K575" s="10" t="inlineStr"/>
+      <c r="L575" s="10" t="inlineStr"/>
+      <c r="M575" s="10" t="inlineStr"/>
+      <c r="N575" s="10" t="inlineStr"/>
+      <c r="O575" s="10" t="inlineStr">
+        <is>
+          <t>SelectValidator</t>
+        </is>
+      </c>
+      <c r="P575" s="10" t="inlineStr"/>
+      <c r="Q575" s="10" t="inlineStr"/>
+      <c r="R575" s="10" t="inlineStr"/>
+      <c r="S575" s="10" t="inlineStr"/>
+      <c r="T575" s="10" t="inlineStr"/>
+      <c r="U575" s="10" t="inlineStr"/>
+    </row>
+    <row r="576" ht="22" customHeight="1">
+      <c r="A576" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::PhotosOfAnyDefectiveItemsDamageOrAreasOfConcern</t>
+        </is>
+      </c>
+      <c r="B576" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C576" s="10" t="inlineStr">
+        <is>
+          <t>PhotosOfAnyDefectiveItemsDamageOrAreasOfConcern</t>
+        </is>
+      </c>
+      <c r="D576" s="10" t="inlineStr">
+        <is>
+          <t>Photos of Any Defective Items, Damage, or Areas of Concern</t>
+        </is>
+      </c>
+      <c r="E576" s="10" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="F576" s="10" t="inlineStr">
+        <is>
+          <t>CameraInput</t>
+        </is>
+      </c>
+      <c r="G576" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H576" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I576" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J576" s="10" t="inlineStr"/>
+      <c r="K576" s="10" t="inlineStr"/>
+      <c r="L576" s="10" t="inlineStr"/>
+      <c r="M576" s="10" t="inlineStr"/>
+      <c r="N576" s="10" t="inlineStr"/>
+      <c r="O576" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P576" s="10" t="inlineStr"/>
+      <c r="Q576" s="10" t="inlineStr"/>
+      <c r="R576" s="10" t="inlineStr"/>
+      <c r="S576" s="10" t="inlineStr"/>
+      <c r="T576" s="10" t="inlineStr"/>
+      <c r="U576" s="10" t="inlineStr"/>
+    </row>
+    <row r="577" ht="22" customHeight="1">
+      <c r="A577" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::AcknowledgementNote</t>
+        </is>
+      </c>
+      <c r="B577" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C577" s="10" t="inlineStr">
+        <is>
+          <t>AcknowledgementNote</t>
+        </is>
+      </c>
+      <c r="D577" s="10" t="inlineStr"/>
+      <c r="E577" s="10" t="inlineStr"/>
+      <c r="F577" s="10" t="inlineStr">
+        <is>
+          <t>StaticText</t>
+        </is>
+      </c>
+      <c r="G577" s="10" t="inlineStr"/>
+      <c r="H577" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I577" s="10" t="inlineStr"/>
+      <c r="J577" s="10" t="inlineStr"/>
+      <c r="K577" s="10" t="inlineStr"/>
+      <c r="L577" s="10" t="inlineStr"/>
+      <c r="M577" s="10" t="inlineStr"/>
+      <c r="N577" s="10" t="inlineStr"/>
+      <c r="O577" s="10" t="inlineStr"/>
+      <c r="P577" s="10" t="inlineStr"/>
+      <c r="Q577" s="10" t="inlineStr"/>
+      <c r="R577" s="10" t="inlineStr"/>
+      <c r="S577" s="10" t="inlineStr"/>
+      <c r="T577" s="10" t="inlineStr"/>
+      <c r="U577" s="10" t="inlineStr"/>
+    </row>
+    <row r="578" ht="22" customHeight="1">
+      <c r="A578" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::EmployeeNameText</t>
+        </is>
+      </c>
+      <c r="B578" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C578" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeNameText</t>
+        </is>
+      </c>
+      <c r="D578" s="10" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="E578" s="10" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="F578" s="10" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="G578" s="10" t="inlineStr"/>
+      <c r="H578" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I578" s="10" t="inlineStr"/>
+      <c r="J578" s="10" t="inlineStr"/>
+      <c r="K578" s="10" t="inlineStr"/>
+      <c r="L578" s="10" t="inlineStr"/>
+      <c r="M578" s="10" t="inlineStr"/>
+      <c r="N578" s="10" t="inlineStr"/>
+      <c r="O578" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P578" s="10" t="inlineStr">
+        <is>
+          <t>const SetValue = async (context) =&gt; { //Code Here return context?.Form?.EmployeeInformationPage?.EmployeeName?.Text; }</t>
+        </is>
+      </c>
+      <c r="Q578" s="10" t="inlineStr"/>
+      <c r="R578" s="10" t="inlineStr"/>
+      <c r="S578" s="10" t="inlineStr"/>
+      <c r="T578" s="10" t="inlineStr"/>
+      <c r="U578" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeName</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="22" customHeight="1">
+      <c r="A579" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::Coordinates</t>
+        </is>
+      </c>
+      <c r="B579" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C579" s="10" t="inlineStr">
+        <is>
+          <t>Coordinates</t>
+        </is>
+      </c>
+      <c r="D579" s="10" t="inlineStr">
+        <is>
+          <t>Coordinates</t>
+        </is>
+      </c>
+      <c r="E579" s="10" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F579" s="10" t="inlineStr">
+        <is>
+          <t>Gps</t>
+        </is>
+      </c>
+      <c r="G579" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H579" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I579" s="10" t="inlineStr"/>
+      <c r="J579" s="10" t="inlineStr"/>
+      <c r="K579" s="10" t="inlineStr"/>
+      <c r="L579" s="10" t="inlineStr"/>
+      <c r="M579" s="10" t="inlineStr"/>
+      <c r="N579" s="10" t="inlineStr"/>
+      <c r="O579" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P579" s="10" t="inlineStr"/>
+      <c r="Q579" s="10" t="inlineStr"/>
+      <c r="R579" s="10" t="inlineStr"/>
+      <c r="S579" s="10" t="inlineStr"/>
+      <c r="T579" s="10" t="inlineStr"/>
+      <c r="U579" s="10" t="inlineStr"/>
+    </row>
+    <row r="580" ht="22" customHeight="1">
+      <c r="A580" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::EmployeeSignature</t>
+        </is>
+      </c>
+      <c r="B580" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C580" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeSignature</t>
+        </is>
+      </c>
+      <c r="D580" s="10" t="inlineStr">
+        <is>
+          <t>Employee Signature</t>
+        </is>
+      </c>
+      <c r="E580" s="10" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="F580" s="10" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="G580" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H580" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I580" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J580" s="10" t="inlineStr"/>
+      <c r="K580" s="10" t="inlineStr"/>
+      <c r="L580" s="10" t="inlineStr"/>
+      <c r="M580" s="10" t="inlineStr"/>
+      <c r="N580" s="10" t="inlineStr"/>
+      <c r="O580" s="10" t="inlineStr">
+        <is>
+          <t>FileValidator</t>
+        </is>
+      </c>
+      <c r="P580" s="10" t="inlineStr"/>
+      <c r="Q580" s="10" t="inlineStr"/>
+      <c r="R580" s="10" t="inlineStr"/>
+      <c r="S580" s="10" t="inlineStr"/>
+      <c r="T580" s="10" t="inlineStr"/>
+      <c r="U580" s="10" t="inlineStr"/>
+    </row>
+    <row r="581" ht="22" customHeight="1">
+      <c r="A581" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::SignatureDate</t>
+        </is>
+      </c>
+      <c r="B581" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C581" s="10" t="inlineStr">
+        <is>
+          <t>SignatureDate</t>
+        </is>
+      </c>
+      <c r="D581" s="10" t="inlineStr">
+        <is>
+          <t>Signature Date</t>
+        </is>
+      </c>
+      <c r="E581" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F581" s="10" t="inlineStr">
+        <is>
+          <t>DateInput</t>
+        </is>
+      </c>
+      <c r="G581" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H581" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I581" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J581" s="10" t="inlineStr"/>
+      <c r="K581" s="10" t="inlineStr"/>
+      <c r="L581" s="10" t="inlineStr"/>
+      <c r="M581" s="10" t="inlineStr"/>
+      <c r="N581" s="10" t="inlineStr"/>
+      <c r="O581" s="10" t="inlineStr">
+        <is>
+          <t>DateValidator</t>
+        </is>
+      </c>
+      <c r="P581" s="10" t="inlineStr"/>
+      <c r="Q581" s="10" t="inlineStr"/>
+      <c r="R581" s="10" t="inlineStr"/>
+      <c r="S581" s="10" t="inlineStr"/>
+      <c r="T581" s="10" t="inlineStr"/>
+      <c r="U581" s="10" t="inlineStr"/>
+    </row>
+    <row r="582" ht="22" customHeight="1">
+      <c r="A582" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection::Location</t>
+        </is>
+      </c>
+      <c r="B582" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle Inspection</t>
+        </is>
+      </c>
+      <c r="C582" s="10" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D582" s="10" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E582" s="10" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F582" s="10" t="inlineStr">
+        <is>
+          <t>Gps</t>
+        </is>
+      </c>
+      <c r="G582" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H582" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I582" s="10" t="inlineStr"/>
+      <c r="J582" s="10" t="inlineStr"/>
+      <c r="K582" s="10" t="inlineStr"/>
+      <c r="L582" s="10" t="inlineStr"/>
+      <c r="M582" s="10" t="inlineStr"/>
+      <c r="N582" s="10" t="inlineStr"/>
+      <c r="O582" s="10" t="inlineStr">
+        <is>
+          <t>StringValidator</t>
+        </is>
+      </c>
+      <c r="P582" s="10" t="inlineStr"/>
+      <c r="Q582" s="10" t="inlineStr"/>
+      <c r="R582" s="10" t="inlineStr"/>
+      <c r="S582" s="10" t="inlineStr"/>
+      <c r="T582" s="10" t="inlineStr"/>
+      <c r="U582" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:U471"/>
+  <autoFilter ref="A3:U582"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -19,7 +19,7 @@
     <sheet name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forms'!$A$3:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forms'!$A$3:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fields'!$A$3:$AB$574</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FormRelationships'!$A$3:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ReferencedDataFields'!$A$3:$F$13</definedName>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -847,8 +847,10 @@
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -901,10 +903,20 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>PriorVersions</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
           <t>SourceFile</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -953,10 +965,20 @@
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
+          <t>Active design export version (_vNN)</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Superseded exports kept on file</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
           <t>Source JSON file (or empty if no profile yet)</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>Free-form</t>
         </is>
@@ -993,12 +1015,16 @@
           <t>2: View All, User | View All</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement_895-installation_warranty_v5_design.json</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -1023,12 +1049,14 @@
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr"/>
+      <c r="L6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -1057,12 +1085,14 @@
           <t>1: View All</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr"/>
+      <c r="L7" s="10" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
@@ -1087,12 +1117,14 @@
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr"/>
+      <c r="L8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -1125,12 +1157,14 @@
           <t>3: View All, Refrigerator | View All, Dishwasher | View All</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr"/>
+      <c r="L9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -1159,12 +1193,14 @@
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -1189,12 +1225,14 @@
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr"/>
       <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr"/>
+      <c r="L11" s="10" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -1223,12 +1261,14 @@
           <t>1: View All</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr"/>
+      <c r="L12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -1253,12 +1293,14 @@
       <c r="F13" s="10" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr"/>
       <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -1283,15 +1325,17 @@
       <c r="F14" s="10" t="inlineStr"/>
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr"/>
+      <c r="L14" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J14"/>
+  <autoFilter ref="A3:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -26,7 +26,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflows'!$A$3:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Triggers'!$A$3:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Actions'!$A$3:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'WorkflowFieldUsage'!$A$3:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'BusinessProcesses'!$A$3:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +99,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00ECEFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -29715,7 +29714,7 @@
     <row r="412" ht="22" customHeight="1">
       <c r="A412" s="10" t="inlineStr">
         <is>
-          <t>Measures::AdditionalFilter</t>
+          <t>Measures::AuditMeasure</t>
         </is>
       </c>
       <c r="B412" s="10" t="inlineStr">
@@ -29725,17 +29724,17 @@
       </c>
       <c r="C412" s="10" t="inlineStr">
         <is>
-          <t>AdditionalFilter</t>
+          <t>AuditMeasure</t>
         </is>
       </c>
       <c r="D412" s="10" t="inlineStr">
         <is>
-          <t>Additional Filter</t>
+          <t>Audit Measure</t>
         </is>
       </c>
       <c r="E412" s="10" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F412" s="10" t="inlineStr"/>
@@ -29765,7 +29764,7 @@
     <row r="413" ht="22" customHeight="1">
       <c r="A413" s="10" t="inlineStr">
         <is>
-          <t>Measures::Deemed2BLkWSavings</t>
+          <t>Measures::CustomParameters</t>
         </is>
       </c>
       <c r="B413" s="10" t="inlineStr">
@@ -29775,17 +29774,17 @@
       </c>
       <c r="C413" s="10" t="inlineStr">
         <is>
-          <t>Deemed2BLkWSavings</t>
+          <t>CustomParameters</t>
         </is>
       </c>
       <c r="D413" s="10" t="inlineStr">
         <is>
-          <t>Deemed 2BL kW Savings</t>
+          <t>Custom Parameters</t>
         </is>
       </c>
       <c r="E413" s="10" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F413" s="10" t="inlineStr"/>
@@ -29815,7 +29814,7 @@
     <row r="414" ht="22" customHeight="1">
       <c r="A414" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureQuantityUnits</t>
+          <t>Measures::Cost</t>
         </is>
       </c>
       <c r="B414" s="10" t="inlineStr">
@@ -29825,17 +29824,17 @@
       </c>
       <c r="C414" s="10" t="inlineStr">
         <is>
-          <t>MeasureQuantityUnits</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="D414" s="10" t="inlineStr">
         <is>
-          <t>Quantity Units</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="E414" s="10" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Calculation</t>
         </is>
       </c>
       <c r="F414" s="10" t="inlineStr"/>
@@ -29865,7 +29864,7 @@
     <row r="415" ht="22" customHeight="1">
       <c r="A415" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureVariant</t>
+          <t>Measures::MaterialCost</t>
         </is>
       </c>
       <c r="B415" s="10" t="inlineStr">
@@ -29875,17 +29874,17 @@
       </c>
       <c r="C415" s="10" t="inlineStr">
         <is>
-          <t>MeasureVariant</t>
+          <t>MaterialCost</t>
         </is>
       </c>
       <c r="D415" s="10" t="inlineStr">
         <is>
-          <t>Variant</t>
+          <t>Material Cost</t>
         </is>
       </c>
       <c r="E415" s="10" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="F415" s="10" t="inlineStr"/>
@@ -29915,7 +29914,7 @@
     <row r="416" ht="22" customHeight="1">
       <c r="A416" s="10" t="inlineStr">
         <is>
-          <t>Measures::MaterialCost</t>
+          <t>Measures::DeemedkWSavings</t>
         </is>
       </c>
       <c r="B416" s="10" t="inlineStr">
@@ -29925,12 +29924,12 @@
       </c>
       <c r="C416" s="10" t="inlineStr">
         <is>
-          <t>MaterialCost</t>
+          <t>DeemedkWSavings</t>
         </is>
       </c>
       <c r="D416" s="10" t="inlineStr">
         <is>
-          <t>Material Cost</t>
+          <t>Deemed kW Savings</t>
         </is>
       </c>
       <c r="E416" s="10" t="inlineStr">
@@ -29965,7 +29964,7 @@
     <row r="417" ht="22" customHeight="1">
       <c r="A417" s="10" t="inlineStr">
         <is>
-          <t>Measures::SnuggProName</t>
+          <t>Measures::ReserveAmount</t>
         </is>
       </c>
       <c r="B417" s="10" t="inlineStr">
@@ -29975,17 +29974,17 @@
       </c>
       <c r="C417" s="10" t="inlineStr">
         <is>
-          <t>SnuggProName</t>
+          <t>ReserveAmount</t>
         </is>
       </c>
       <c r="D417" s="10" t="inlineStr">
         <is>
-          <t>SnuggPro Name</t>
+          <t>Reserve Amount</t>
         </is>
       </c>
       <c r="E417" s="10" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="F417" s="10" t="inlineStr"/>
@@ -30015,7 +30014,7 @@
     <row r="418" ht="22" customHeight="1">
       <c r="A418" s="10" t="inlineStr">
         <is>
-          <t>Measures::Deemed2BLThermsSavings</t>
+          <t>Measures::LaborCost</t>
         </is>
       </c>
       <c r="B418" s="10" t="inlineStr">
@@ -30025,17 +30024,17 @@
       </c>
       <c r="C418" s="10" t="inlineStr">
         <is>
-          <t>Deemed2BLThermsSavings</t>
+          <t>LaborCost</t>
         </is>
       </c>
       <c r="D418" s="10" t="inlineStr">
         <is>
-          <t>Deemed 2BL Therms Savings</t>
+          <t>Labor Cost</t>
         </is>
       </c>
       <c r="E418" s="10" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="F418" s="10" t="inlineStr"/>
@@ -30065,7 +30064,7 @@
     <row r="419" ht="22" customHeight="1">
       <c r="A419" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureGrouping</t>
+          <t>Measures::AdditionalFilter</t>
         </is>
       </c>
       <c r="B419" s="10" t="inlineStr">
@@ -30075,17 +30074,17 @@
       </c>
       <c r="C419" s="10" t="inlineStr">
         <is>
-          <t>MeasureGrouping</t>
+          <t>AdditionalFilter</t>
         </is>
       </c>
       <c r="D419" s="10" t="inlineStr">
         <is>
-          <t>Measure Grouping</t>
+          <t>Additional Filter</t>
         </is>
       </c>
       <c r="E419" s="10" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>List</t>
         </is>
       </c>
       <c r="F419" s="10" t="inlineStr"/>
@@ -30115,7 +30114,7 @@
     <row r="420" ht="22" customHeight="1">
       <c r="A420" s="10" t="inlineStr">
         <is>
-          <t>Measures::Deemed2BLGallonSavings</t>
+          <t>Measures::Deemed2BLkWSavings</t>
         </is>
       </c>
       <c r="B420" s="10" t="inlineStr">
@@ -30125,12 +30124,12 @@
       </c>
       <c r="C420" s="10" t="inlineStr">
         <is>
-          <t>Deemed2BLGallonSavings</t>
+          <t>Deemed2BLkWSavings</t>
         </is>
       </c>
       <c r="D420" s="10" t="inlineStr">
         <is>
-          <t>Deemed 2BL Gallon Savings</t>
+          <t>Deemed 2BL kW Savings</t>
         </is>
       </c>
       <c r="E420" s="10" t="inlineStr">
@@ -30165,7 +30164,7 @@
     <row r="421" ht="22" customHeight="1">
       <c r="A421" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureReportGroupCode</t>
+          <t>Measures::MeasureQuantityUnits</t>
         </is>
       </c>
       <c r="B421" s="10" t="inlineStr">
@@ -30175,12 +30174,12 @@
       </c>
       <c r="C421" s="10" t="inlineStr">
         <is>
-          <t>MeasureReportGroupCode</t>
+          <t>MeasureQuantityUnits</t>
         </is>
       </c>
       <c r="D421" s="10" t="inlineStr">
         <is>
-          <t>Report Group Code</t>
+          <t>Quantity Units</t>
         </is>
       </c>
       <c r="E421" s="10" t="inlineStr">
@@ -30215,7 +30214,7 @@
     <row r="422" ht="22" customHeight="1">
       <c r="A422" s="10" t="inlineStr">
         <is>
-          <t>Measures::IOU</t>
+          <t>Measures::MeasureVariant</t>
         </is>
       </c>
       <c r="B422" s="10" t="inlineStr">
@@ -30225,12 +30224,12 @@
       </c>
       <c r="C422" s="10" t="inlineStr">
         <is>
-          <t>IOU</t>
+          <t>MeasureVariant</t>
         </is>
       </c>
       <c r="D422" s="10" t="inlineStr">
         <is>
-          <t>IOU</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="E422" s="10" t="inlineStr">
@@ -30265,7 +30264,7 @@
     <row r="423" ht="22" customHeight="1">
       <c r="A423" s="10" t="inlineStr">
         <is>
-          <t>Measures::DeemedkWSavings</t>
+          <t>Measures::SnuggProName</t>
         </is>
       </c>
       <c r="B423" s="10" t="inlineStr">
@@ -30275,17 +30274,17 @@
       </c>
       <c r="C423" s="10" t="inlineStr">
         <is>
-          <t>DeemedkWSavings</t>
+          <t>SnuggProName</t>
         </is>
       </c>
       <c r="D423" s="10" t="inlineStr">
         <is>
-          <t>Deemed kW Savings</t>
+          <t>SnuggPro Name</t>
         </is>
       </c>
       <c r="E423" s="10" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F423" s="10" t="inlineStr"/>
@@ -30315,7 +30314,7 @@
     <row r="424" ht="22" customHeight="1">
       <c r="A424" s="10" t="inlineStr">
         <is>
-          <t>Measures::AuditMeasure</t>
+          <t>Measures::Deemed2BLThermsSavings</t>
         </is>
       </c>
       <c r="B424" s="10" t="inlineStr">
@@ -30325,17 +30324,17 @@
       </c>
       <c r="C424" s="10" t="inlineStr">
         <is>
-          <t>AuditMeasure</t>
+          <t>Deemed2BLThermsSavings</t>
         </is>
       </c>
       <c r="D424" s="10" t="inlineStr">
         <is>
-          <t>Audit Measure</t>
+          <t>Deemed 2BL Therms Savings</t>
         </is>
       </c>
       <c r="E424" s="10" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F424" s="10" t="inlineStr"/>
@@ -30365,7 +30364,7 @@
     <row r="425" ht="22" customHeight="1">
       <c r="A425" s="10" t="inlineStr">
         <is>
-          <t>Measures::FuelType</t>
+          <t>Measures::MeasureGrouping</t>
         </is>
       </c>
       <c r="B425" s="10" t="inlineStr">
@@ -30375,12 +30374,12 @@
       </c>
       <c r="C425" s="10" t="inlineStr">
         <is>
-          <t>FuelType</t>
+          <t>MeasureGrouping</t>
         </is>
       </c>
       <c r="D425" s="10" t="inlineStr">
         <is>
-          <t>Fuel Type</t>
+          <t>Measure Grouping</t>
         </is>
       </c>
       <c r="E425" s="10" t="inlineStr">
@@ -30415,7 +30414,7 @@
     <row r="426" ht="22" customHeight="1">
       <c r="A426" s="10" t="inlineStr">
         <is>
-          <t>Measures::TotalCO2SavingsMT</t>
+          <t>Measures::Deemed2BLGallonSavings</t>
         </is>
       </c>
       <c r="B426" s="10" t="inlineStr">
@@ -30425,12 +30424,12 @@
       </c>
       <c r="C426" s="10" t="inlineStr">
         <is>
-          <t>TotalCO2SavingsMT</t>
+          <t>Deemed2BLGallonSavings</t>
         </is>
       </c>
       <c r="D426" s="10" t="inlineStr">
         <is>
-          <t>Total CO2 Savings (MT)</t>
+          <t>Deemed 2BL Gallon Savings</t>
         </is>
       </c>
       <c r="E426" s="10" t="inlineStr">
@@ -30465,7 +30464,7 @@
     <row r="427" ht="22" customHeight="1">
       <c r="A427" s="10" t="inlineStr">
         <is>
-          <t>Measures::DeemedThermsSavings</t>
+          <t>Measures::MeasureReportGroupCode</t>
         </is>
       </c>
       <c r="B427" s="10" t="inlineStr">
@@ -30475,12 +30474,12 @@
       </c>
       <c r="C427" s="10" t="inlineStr">
         <is>
-          <t>DeemedThermsSavings</t>
+          <t>MeasureReportGroupCode</t>
         </is>
       </c>
       <c r="D427" s="10" t="inlineStr">
         <is>
-          <t>Deemed Therms Savings</t>
+          <t>Report Group Code</t>
         </is>
       </c>
       <c r="E427" s="10" t="inlineStr">
@@ -30515,7 +30514,7 @@
     <row r="428" ht="22" customHeight="1">
       <c r="A428" s="10" t="inlineStr">
         <is>
-          <t>Measures::ExternalId</t>
+          <t>Measures::IOU</t>
         </is>
       </c>
       <c r="B428" s="10" t="inlineStr">
@@ -30525,12 +30524,12 @@
       </c>
       <c r="C428" s="10" t="inlineStr">
         <is>
-          <t>ExternalId</t>
+          <t>IOU</t>
         </is>
       </c>
       <c r="D428" s="10" t="inlineStr">
         <is>
-          <t>External ID</t>
+          <t>IOU</t>
         </is>
       </c>
       <c r="E428" s="10" t="inlineStr">
@@ -30565,7 +30564,7 @@
     <row r="429" ht="22" customHeight="1">
       <c r="A429" s="10" t="inlineStr">
         <is>
-          <t>Measures::DeemedkWhSavings</t>
+          <t>Measures::FuelType</t>
         </is>
       </c>
       <c r="B429" s="10" t="inlineStr">
@@ -30575,12 +30574,12 @@
       </c>
       <c r="C429" s="10" t="inlineStr">
         <is>
-          <t>DeemedkWhSavings</t>
+          <t>FuelType</t>
         </is>
       </c>
       <c r="D429" s="10" t="inlineStr">
         <is>
-          <t>Deemed kWh Savings</t>
+          <t>Fuel Type</t>
         </is>
       </c>
       <c r="E429" s="10" t="inlineStr">
@@ -30615,7 +30614,7 @@
     <row r="430" ht="22" customHeight="1">
       <c r="A430" s="10" t="inlineStr">
         <is>
-          <t>Measures::Capacity</t>
+          <t>Measures::TotalCO2SavingsMT</t>
         </is>
       </c>
       <c r="B430" s="10" t="inlineStr">
@@ -30625,12 +30624,12 @@
       </c>
       <c r="C430" s="10" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>TotalCO2SavingsMT</t>
         </is>
       </c>
       <c r="D430" s="10" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Total CO2 Savings (MT)</t>
         </is>
       </c>
       <c r="E430" s="10" t="inlineStr">
@@ -30665,7 +30664,7 @@
     <row r="431" ht="22" customHeight="1">
       <c r="A431" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureDownpayment</t>
+          <t>Measures::DeemedThermsSavings</t>
         </is>
       </c>
       <c r="B431" s="10" t="inlineStr">
@@ -30675,12 +30674,12 @@
       </c>
       <c r="C431" s="10" t="inlineStr">
         <is>
-          <t>MeasureDownpayment</t>
+          <t>DeemedThermsSavings</t>
         </is>
       </c>
       <c r="D431" s="10" t="inlineStr">
         <is>
-          <t>Down Payment</t>
+          <t>Deemed Therms Savings</t>
         </is>
       </c>
       <c r="E431" s="10" t="inlineStr">
@@ -30715,7 +30714,7 @@
     <row r="432" ht="22" customHeight="1">
       <c r="A432" s="10" t="inlineStr">
         <is>
-          <t>Measures::SavingsUnit</t>
+          <t>Measures::ExternalId</t>
         </is>
       </c>
       <c r="B432" s="10" t="inlineStr">
@@ -30725,12 +30724,12 @@
       </c>
       <c r="C432" s="10" t="inlineStr">
         <is>
-          <t>SavingsUnit</t>
+          <t>ExternalId</t>
         </is>
       </c>
       <c r="D432" s="10" t="inlineStr">
         <is>
-          <t>Savings Unit</t>
+          <t>External ID</t>
         </is>
       </c>
       <c r="E432" s="10" t="inlineStr">
@@ -30765,7 +30764,7 @@
     <row r="433" ht="22" customHeight="1">
       <c r="A433" s="10" t="inlineStr">
         <is>
-          <t>Measures::ReserveAmount</t>
+          <t>Measures::DeemedkWhSavings</t>
         </is>
       </c>
       <c r="B433" s="10" t="inlineStr">
@@ -30775,17 +30774,17 @@
       </c>
       <c r="C433" s="10" t="inlineStr">
         <is>
-          <t>ReserveAmount</t>
+          <t>DeemedkWhSavings</t>
         </is>
       </c>
       <c r="D433" s="10" t="inlineStr">
         <is>
-          <t>Reserve Amount</t>
+          <t>Deemed kWh Savings</t>
         </is>
       </c>
       <c r="E433" s="10" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F433" s="10" t="inlineStr"/>
@@ -30815,7 +30814,7 @@
     <row r="434" ht="22" customHeight="1">
       <c r="A434" s="10" t="inlineStr">
         <is>
-          <t>Measures::BulkPurchase</t>
+          <t>Measures::Capacity</t>
         </is>
       </c>
       <c r="B434" s="10" t="inlineStr">
@@ -30825,12 +30824,12 @@
       </c>
       <c r="C434" s="10" t="inlineStr">
         <is>
-          <t>BulkPurchase</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="D434" s="10" t="inlineStr">
         <is>
-          <t>Bulk Purchase</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="E434" s="10" t="inlineStr">
@@ -30865,7 +30864,7 @@
     <row r="435" ht="22" customHeight="1">
       <c r="A435" s="10" t="inlineStr">
         <is>
-          <t>Measures::DeemedMMBTU</t>
+          <t>Measures::MeasureDownpayment</t>
         </is>
       </c>
       <c r="B435" s="10" t="inlineStr">
@@ -30875,12 +30874,12 @@
       </c>
       <c r="C435" s="10" t="inlineStr">
         <is>
-          <t>DeemedMMBTU</t>
+          <t>MeasureDownpayment</t>
         </is>
       </c>
       <c r="D435" s="10" t="inlineStr">
         <is>
-          <t>Deemed MMBTU</t>
+          <t>Down Payment</t>
         </is>
       </c>
       <c r="E435" s="10" t="inlineStr">
@@ -30915,7 +30914,7 @@
     <row r="436" ht="22" customHeight="1">
       <c r="A436" s="10" t="inlineStr">
         <is>
-          <t>Measures::LaborCost</t>
+          <t>Measures::SavingsUnit</t>
         </is>
       </c>
       <c r="B436" s="10" t="inlineStr">
@@ -30925,17 +30924,17 @@
       </c>
       <c r="C436" s="10" t="inlineStr">
         <is>
-          <t>LaborCost</t>
+          <t>SavingsUnit</t>
         </is>
       </c>
       <c r="D436" s="10" t="inlineStr">
         <is>
-          <t>Labor Cost</t>
+          <t>Savings Unit</t>
         </is>
       </c>
       <c r="E436" s="10" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F436" s="10" t="inlineStr"/>
@@ -30965,7 +30964,7 @@
     <row r="437" ht="22" customHeight="1">
       <c r="A437" s="10" t="inlineStr">
         <is>
-          <t>Measures::ExistingFuelType</t>
+          <t>Measures::BulkPurchase</t>
         </is>
       </c>
       <c r="B437" s="10" t="inlineStr">
@@ -30975,12 +30974,12 @@
       </c>
       <c r="C437" s="10" t="inlineStr">
         <is>
-          <t>ExistingFuelType</t>
+          <t>BulkPurchase</t>
         </is>
       </c>
       <c r="D437" s="10" t="inlineStr">
         <is>
-          <t>Existing Fuel Type</t>
+          <t>Bulk Purchase</t>
         </is>
       </c>
       <c r="E437" s="10" t="inlineStr">
@@ -31015,7 +31014,7 @@
     <row r="438" ht="22" customHeight="1">
       <c r="A438" s="10" t="inlineStr">
         <is>
-          <t>Measures::Category</t>
+          <t>Measures::DeemedMMBTU</t>
         </is>
       </c>
       <c r="B438" s="10" t="inlineStr">
@@ -31025,12 +31024,12 @@
       </c>
       <c r="C438" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>DeemedMMBTU</t>
         </is>
       </c>
       <c r="D438" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Deemed MMBTU</t>
         </is>
       </c>
       <c r="E438" s="10" t="inlineStr">
@@ -31065,7 +31064,7 @@
     <row r="439" ht="22" customHeight="1">
       <c r="A439" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureCostNTE</t>
+          <t>Measures::ExistingFuelType</t>
         </is>
       </c>
       <c r="B439" s="10" t="inlineStr">
@@ -31075,12 +31074,12 @@
       </c>
       <c r="C439" s="10" t="inlineStr">
         <is>
-          <t>MeasureCostNTE</t>
+          <t>ExistingFuelType</t>
         </is>
       </c>
       <c r="D439" s="10" t="inlineStr">
         <is>
-          <t>Measure Cost (Not To Exceed)</t>
+          <t>Existing Fuel Type</t>
         </is>
       </c>
       <c r="E439" s="10" t="inlineStr">
@@ -31115,7 +31114,7 @@
     <row r="440" ht="22" customHeight="1">
       <c r="A440" s="10" t="inlineStr">
         <is>
-          <t>Measures::EULYears</t>
+          <t>Measures::Category</t>
         </is>
       </c>
       <c r="B440" s="10" t="inlineStr">
@@ -31125,12 +31124,12 @@
       </c>
       <c r="C440" s="10" t="inlineStr">
         <is>
-          <t>EULYears</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D440" s="10" t="inlineStr">
         <is>
-          <t>EUL (Years)</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E440" s="10" t="inlineStr">
@@ -31165,7 +31164,7 @@
     <row r="441" ht="22" customHeight="1">
       <c r="A441" s="10" t="inlineStr">
         <is>
-          <t>Measures::AFUE</t>
+          <t>Measures::MeasureCostNTE</t>
         </is>
       </c>
       <c r="B441" s="10" t="inlineStr">
@@ -31175,12 +31174,12 @@
       </c>
       <c r="C441" s="10" t="inlineStr">
         <is>
-          <t>AFUE</t>
+          <t>MeasureCostNTE</t>
         </is>
       </c>
       <c r="D441" s="10" t="inlineStr">
         <is>
-          <t>AFUE</t>
+          <t>Measure Cost (Not To Exceed)</t>
         </is>
       </c>
       <c r="E441" s="10" t="inlineStr">
@@ -31215,7 +31214,7 @@
     <row r="442" ht="22" customHeight="1">
       <c r="A442" s="10" t="inlineStr">
         <is>
-          <t>Measures::UEF</t>
+          <t>Measures::EULYears</t>
         </is>
       </c>
       <c r="B442" s="10" t="inlineStr">
@@ -31225,12 +31224,12 @@
       </c>
       <c r="C442" s="10" t="inlineStr">
         <is>
-          <t>UEF</t>
+          <t>EULYears</t>
         </is>
       </c>
       <c r="D442" s="10" t="inlineStr">
         <is>
-          <t>UEF</t>
+          <t>EUL (Years)</t>
         </is>
       </c>
       <c r="E442" s="10" t="inlineStr">
@@ -31265,7 +31264,7 @@
     <row r="443" ht="22" customHeight="1">
       <c r="A443" s="10" t="inlineStr">
         <is>
-          <t>Measures::Variation</t>
+          <t>Measures::AFUE</t>
         </is>
       </c>
       <c r="B443" s="10" t="inlineStr">
@@ -31275,12 +31274,12 @@
       </c>
       <c r="C443" s="10" t="inlineStr">
         <is>
-          <t>Variation</t>
+          <t>AFUE</t>
         </is>
       </c>
       <c r="D443" s="10" t="inlineStr">
         <is>
-          <t>Variation</t>
+          <t>AFUE</t>
         </is>
       </c>
       <c r="E443" s="10" t="inlineStr">
@@ -31315,7 +31314,7 @@
     <row r="444" ht="22" customHeight="1">
       <c r="A444" s="10" t="inlineStr">
         <is>
-          <t>Measures::InsulationRValue</t>
+          <t>Measures::UEF</t>
         </is>
       </c>
       <c r="B444" s="10" t="inlineStr">
@@ -31325,12 +31324,12 @@
       </c>
       <c r="C444" s="10" t="inlineStr">
         <is>
-          <t>InsulationRValue</t>
+          <t>UEF</t>
         </is>
       </c>
       <c r="D444" s="10" t="inlineStr">
         <is>
-          <t>R-Value</t>
+          <t>UEF</t>
         </is>
       </c>
       <c r="E444" s="10" t="inlineStr">
@@ -31365,7 +31364,7 @@
     <row r="445" ht="22" customHeight="1">
       <c r="A445" s="10" t="inlineStr">
         <is>
-          <t>Measures::Deemed2BLkWhSavings</t>
+          <t>Measures::Variation</t>
         </is>
       </c>
       <c r="B445" s="10" t="inlineStr">
@@ -31375,12 +31374,12 @@
       </c>
       <c r="C445" s="10" t="inlineStr">
         <is>
-          <t>Deemed2BLkWhSavings</t>
+          <t>Variation</t>
         </is>
       </c>
       <c r="D445" s="10" t="inlineStr">
         <is>
-          <t>Deemed 2BL kWh Savings</t>
+          <t>Variation</t>
         </is>
       </c>
       <c r="E445" s="10" t="inlineStr">
@@ -31415,7 +31414,7 @@
     <row r="446" ht="22" customHeight="1">
       <c r="A446" s="10" t="inlineStr">
         <is>
-          <t>Measures::ReportMeasureName</t>
+          <t>Measures::InsulationRValue</t>
         </is>
       </c>
       <c r="B446" s="10" t="inlineStr">
@@ -31425,12 +31424,12 @@
       </c>
       <c r="C446" s="10" t="inlineStr">
         <is>
-          <t>ReportMeasureName</t>
+          <t>InsulationRValue</t>
         </is>
       </c>
       <c r="D446" s="10" t="inlineStr">
         <is>
-          <t>Report Measure Name</t>
+          <t>R-Value</t>
         </is>
       </c>
       <c r="E446" s="10" t="inlineStr">
@@ -31465,7 +31464,7 @@
     <row r="447" ht="22" customHeight="1">
       <c r="A447" s="10" t="inlineStr">
         <is>
-          <t>Measures::PathRestriction</t>
+          <t>Measures::Deemed2BLkWhSavings</t>
         </is>
       </c>
       <c r="B447" s="10" t="inlineStr">
@@ -31475,12 +31474,12 @@
       </c>
       <c r="C447" s="10" t="inlineStr">
         <is>
-          <t>PathRestriction</t>
+          <t>Deemed2BLkWhSavings</t>
         </is>
       </c>
       <c r="D447" s="10" t="inlineStr">
         <is>
-          <t>Path Restriction</t>
+          <t>Deemed 2BL kWh Savings</t>
         </is>
       </c>
       <c r="E447" s="10" t="inlineStr">
@@ -31515,7 +31514,7 @@
     <row r="448" ht="22" customHeight="1">
       <c r="A448" s="10" t="inlineStr">
         <is>
-          <t>Measures::EULMonths</t>
+          <t>Measures::ReportMeasureName</t>
         </is>
       </c>
       <c r="B448" s="10" t="inlineStr">
@@ -31525,12 +31524,12 @@
       </c>
       <c r="C448" s="10" t="inlineStr">
         <is>
-          <t>EULMonths</t>
+          <t>ReportMeasureName</t>
         </is>
       </c>
       <c r="D448" s="10" t="inlineStr">
         <is>
-          <t>EUL (Months)</t>
+          <t>Report Measure Name</t>
         </is>
       </c>
       <c r="E448" s="10" t="inlineStr">
@@ -31565,7 +31564,7 @@
     <row r="449" ht="22" customHeight="1">
       <c r="A449" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureReportGroup</t>
+          <t>Measures::PathRestriction</t>
         </is>
       </c>
       <c r="B449" s="10" t="inlineStr">
@@ -31575,12 +31574,12 @@
       </c>
       <c r="C449" s="10" t="inlineStr">
         <is>
-          <t>MeasureReportGroup</t>
+          <t>PathRestriction</t>
         </is>
       </c>
       <c r="D449" s="10" t="inlineStr">
         <is>
-          <t>Measure Report Group</t>
+          <t>Path Restriction</t>
         </is>
       </c>
       <c r="E449" s="10" t="inlineStr">
@@ -31615,7 +31614,7 @@
     <row r="450" ht="22" customHeight="1">
       <c r="A450" s="10" t="inlineStr">
         <is>
-          <t>Measures::Tons</t>
+          <t>Measures::EULMonths</t>
         </is>
       </c>
       <c r="B450" s="10" t="inlineStr">
@@ -31625,12 +31624,12 @@
       </c>
       <c r="C450" s="10" t="inlineStr">
         <is>
-          <t>Tons</t>
+          <t>EULMonths</t>
         </is>
       </c>
       <c r="D450" s="10" t="inlineStr">
         <is>
-          <t>Tons</t>
+          <t>EUL (Months)</t>
         </is>
       </c>
       <c r="E450" s="10" t="inlineStr">
@@ -31665,7 +31664,7 @@
     <row r="451" ht="22" customHeight="1">
       <c r="A451" s="10" t="inlineStr">
         <is>
-          <t>Measures::HVACType</t>
+          <t>Measures::MeasureReportGroup</t>
         </is>
       </c>
       <c r="B451" s="10" t="inlineStr">
@@ -31675,12 +31674,12 @@
       </c>
       <c r="C451" s="10" t="inlineStr">
         <is>
-          <t>HVACType</t>
+          <t>MeasureReportGroup</t>
         </is>
       </c>
       <c r="D451" s="10" t="inlineStr">
         <is>
-          <t>HVAC Type</t>
+          <t>Measure Report Group</t>
         </is>
       </c>
       <c r="E451" s="10" t="inlineStr">
@@ -31715,7 +31714,7 @@
     <row r="452" ht="22" customHeight="1">
       <c r="A452" s="10" t="inlineStr">
         <is>
-          <t>Measures::Cost</t>
+          <t>Measures::Tons</t>
         </is>
       </c>
       <c r="B452" s="10" t="inlineStr">
@@ -31725,17 +31724,17 @@
       </c>
       <c r="C452" s="10" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Tons</t>
         </is>
       </c>
       <c r="D452" s="10" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Tons</t>
         </is>
       </c>
       <c r="E452" s="10" t="inlineStr">
         <is>
-          <t>Calculation</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F452" s="10" t="inlineStr"/>
@@ -31765,7 +31764,7 @@
     <row r="453" ht="22" customHeight="1">
       <c r="A453" s="10" t="inlineStr">
         <is>
-          <t>Measures::ReportMeasureCategory</t>
+          <t>Measures::HVACType</t>
         </is>
       </c>
       <c r="B453" s="10" t="inlineStr">
@@ -31775,12 +31774,12 @@
       </c>
       <c r="C453" s="10" t="inlineStr">
         <is>
-          <t>ReportMeasureCategory</t>
+          <t>HVACType</t>
         </is>
       </c>
       <c r="D453" s="10" t="inlineStr">
         <is>
-          <t>Report Measure Category</t>
+          <t>HVAC Type</t>
         </is>
       </c>
       <c r="E453" s="10" t="inlineStr">
@@ -31815,7 +31814,7 @@
     <row r="454" ht="22" customHeight="1">
       <c r="A454" s="10" t="inlineStr">
         <is>
-          <t>Measures::CostUnit</t>
+          <t>Measures::ReportMeasureCategory</t>
         </is>
       </c>
       <c r="B454" s="10" t="inlineStr">
@@ -31825,12 +31824,12 @@
       </c>
       <c r="C454" s="10" t="inlineStr">
         <is>
-          <t>CostUnit</t>
+          <t>ReportMeasureCategory</t>
         </is>
       </c>
       <c r="D454" s="10" t="inlineStr">
         <is>
-          <t>Cost Unit</t>
+          <t>Report Measure Category</t>
         </is>
       </c>
       <c r="E454" s="10" t="inlineStr">
@@ -31865,7 +31864,7 @@
     <row r="455" ht="22" customHeight="1">
       <c r="A455" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureFilter</t>
+          <t>Measures::CostUnit</t>
         </is>
       </c>
       <c r="B455" s="10" t="inlineStr">
@@ -31875,12 +31874,12 @@
       </c>
       <c r="C455" s="10" t="inlineStr">
         <is>
-          <t>MeasureFilter</t>
+          <t>CostUnit</t>
         </is>
       </c>
       <c r="D455" s="10" t="inlineStr">
         <is>
-          <t>Measure Filter</t>
+          <t>Cost Unit</t>
         </is>
       </c>
       <c r="E455" s="10" t="inlineStr">
@@ -31915,7 +31914,7 @@
     <row r="456" ht="22" customHeight="1">
       <c r="A456" s="10" t="inlineStr">
         <is>
-          <t>Measures::SnuggProCode</t>
+          <t>Measures::MeasureFilter</t>
         </is>
       </c>
       <c r="B456" s="10" t="inlineStr">
@@ -31925,12 +31924,12 @@
       </c>
       <c r="C456" s="10" t="inlineStr">
         <is>
-          <t>SnuggProCode</t>
+          <t>MeasureFilter</t>
         </is>
       </c>
       <c r="D456" s="10" t="inlineStr">
         <is>
-          <t>SnuggPro Code</t>
+          <t>Measure Filter</t>
         </is>
       </c>
       <c r="E456" s="10" t="inlineStr">
@@ -31965,7 +31964,7 @@
     <row r="457" ht="22" customHeight="1">
       <c r="A457" s="10" t="inlineStr">
         <is>
-          <t>Measures::MeasureTypeCode</t>
+          <t>Measures::SnuggProCode</t>
         </is>
       </c>
       <c r="B457" s="10" t="inlineStr">
@@ -31975,12 +31974,12 @@
       </c>
       <c r="C457" s="10" t="inlineStr">
         <is>
-          <t>MeasureTypeCode</t>
+          <t>SnuggProCode</t>
         </is>
       </c>
       <c r="D457" s="10" t="inlineStr">
         <is>
-          <t>Measure Type Code</t>
+          <t>SnuggPro Code</t>
         </is>
       </c>
       <c r="E457" s="10" t="inlineStr">
@@ -32015,7 +32014,7 @@
     <row r="458" ht="22" customHeight="1">
       <c r="A458" s="10" t="inlineStr">
         <is>
-          <t>Measures::DetailedHVACType</t>
+          <t>Measures::MeasureTypeCode</t>
         </is>
       </c>
       <c r="B458" s="10" t="inlineStr">
@@ -32025,12 +32024,12 @@
       </c>
       <c r="C458" s="10" t="inlineStr">
         <is>
-          <t>DetailedHVACType</t>
+          <t>MeasureTypeCode</t>
         </is>
       </c>
       <c r="D458" s="10" t="inlineStr">
         <is>
-          <t>Detailed HVAC Type</t>
+          <t>Measure Type Code</t>
         </is>
       </c>
       <c r="E458" s="10" t="inlineStr">
@@ -32065,7 +32064,7 @@
     <row r="459" ht="22" customHeight="1">
       <c r="A459" s="10" t="inlineStr">
         <is>
-          <t>Measures::CustomParameters</t>
+          <t>Measures::DetailedHVACType</t>
         </is>
       </c>
       <c r="B459" s="10" t="inlineStr">
@@ -32075,17 +32074,17 @@
       </c>
       <c r="C459" s="10" t="inlineStr">
         <is>
-          <t>CustomParameters</t>
+          <t>DetailedHVACType</t>
         </is>
       </c>
       <c r="D459" s="10" t="inlineStr">
         <is>
-          <t>Custom Parameters</t>
+          <t>Detailed HVAC Type</t>
         </is>
       </c>
       <c r="E459" s="10" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F459" s="10" t="inlineStr"/>
@@ -40697,7 +40696,7 @@
           <t>Dispatch to User</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr"/>
+      <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Runs when a new 895 - Installation / Warranty record is created.</t>
@@ -40705,7 +40704,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>WFEngine</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
@@ -40721,7 +40720,11 @@
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>6ab03969-872f-6878-a60c-3a226ee16f94</t>
+        </is>
+      </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
           <t>qualified_appliance_replacement.json</t>
@@ -40920,8 +40923,14 @@
           <t>Create</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Post-processing</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="I5" s="10" t="inlineStr"/>
       <c r="J5" s="10" t="inlineStr"/>
       <c r="K5" s="10" t="inlineStr"/>
@@ -41093,20 +41102,24 @@
           <t>895_DISPATCH_TO_USER</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Send Email</t>
+        </is>
+      </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>QAR Installation {ProjectNumber} - {AddressStreet1}</t>
+          <t>Send Email</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>BuiltIn.SendEmail</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
@@ -41115,7 +41128,7 @@
       <c r="I5" s="10" t="inlineStr"/>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>To: {AssignedUserEmail} · Subject: QAR Installation {ProjectNumber} - {AddressStreet1}</t>
+          <t>To: AssignedUserEmail · Subject: QAR Installation {{ProjectNumber}} - {{AddressStreet1}}</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -41137,7 +41150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -41230,356 +41243,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr"/>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>AddressCity</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>AddressStreet1</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>AddressStreet2</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>AddressZipcode</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>AppointmentWindow</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>AssignedUser</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>AssignedUserEmail</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr"/>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>EmailAddress</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>FirstName</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>LastName</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>PrimaryPhoneNumber</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>895_DISPATCH_TO_USER</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>895 - Installation / Warranty</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>ProjectNumber</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Notification template</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/nve-qar/workflow_master_inventory.xlsx
+++ b/output/nve-qar/workflow_master_inventory.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Forms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fields" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Actions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormRelationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReferencedDataFields" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Triggers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkflowFieldUsage" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BusinessProcesses" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forms'!$A$3:$L$14</definedName>
